--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_audit_log.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_audit_log.xlsx
@@ -913,7 +913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -940,11 +940,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13602</v>
+        <v>14506</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8ba0309e3568e5c4860a71fb4789cd621cc704b6366b86bd23bd8727b87cc84e</t>
+          <t>ccfbca5b9dd57957714bded6fc9e99e6d502b16e91c7896ad0347d8f3658f0f3</t>
         </is>
       </c>
     </row>
@@ -955,11 +955,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2382</v>
+        <v>3200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>89d5b54cdb4b970d95acb829f7ddf6eb230b270d6000dd8c87047f29c6f1c3d4</t>
+          <t>a12d21fd62dd04f5d6dcd660f41bde69f941e4f4a9ccf1cda2e1623d61089a32</t>
         </is>
       </c>
     </row>
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>49208</v>
+        <v>51706</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>309e462028bd4b6ff796d4c6627f36a4e82d665afe6c29d07dfd70f5866257a1</t>
+          <t>2f1abed0142d2617649cf488d33cfc996ab0cd89c918d15788226139201b978c</t>
         </is>
       </c>
     </row>
@@ -985,11 +985,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>282038</v>
+        <v>315954</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3d4abf7093191a47db0e323225200ccf9f03106afb818dade304137401ebb469</t>
+          <t>b8d6b85f4de5f3b1fa8eaf072ceb49e927f0936e248b69ce8363889076a5dfc2</t>
         </is>
       </c>
     </row>
@@ -1000,924 +1000,999 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37998</v>
+        <v>28772</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bc3f147b7b79ae412151717ff8450396368a89451ae38599788c12fb1ff8d96f</t>
+          <t>a1ad2baf716112cb511807d080f4a6eef164ce779dbdf1736c817fbf69c8af67</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD7_2_spatiotemporal.pdf</t>
+          <t>outputs/figures/FigD7_1_framework.tiff</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>68792</v>
+        <v>620316</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0730bb25fb25f32f10f8ca24bbe9ffcb7268dc65daced0447ad91b523fe874b6</t>
+          <t>fa89c5f1fb49f0ad9ee0978df75a4d2aeab0bfb4d14efd1ebc9c6e0c78c44f25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD7_2_spatiotemporal.png</t>
+          <t>outputs/figures/FigD7_2_spatiotemporal.pdf</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>345707</v>
+        <v>63355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>54df2039c1f7089650f77d0290fc425757a27b3fca852bcf4a65fa8e44837889</t>
+          <t>14290cb202b7cfe5dcdca221de89023aabd324fded52f87c207f9173df0784ba</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD7_2_spatiotemporal.svg</t>
+          <t>outputs/figures/FigD7_2_spatiotemporal.png</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70324</v>
+        <v>385799</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>d3ad18ca714624bfc20b20ca22f7c5933af77ffa342eb789474953970cd7246d</t>
+          <t>055f03c1decf7348eb20b879356faaadb23329fe9a86f9f1803d8ff3444a4b88</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD7_3_evidence.pdf</t>
+          <t>outputs/figures/FigD7_2_spatiotemporal.svg</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54403</v>
+        <v>69127</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8a9e29f8a55d2c569e2767104100b48bdffd8ac81de2b8012206269c19da90ce</t>
+          <t>7cdf92f33c51439e135456d40a72a2da7dd470ec6d5b25c5e97cca5db13c0915</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD7_3_evidence.png</t>
+          <t>outputs/figures/FigD7_2_spatiotemporal.tiff</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>573661</v>
+        <v>7350736</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>a2db09eaeb1480d9fb757d780c4447c44585ec534a7eba04524acd5167011179</t>
+          <t>35c45a2caff1b1f979ff182f6e44550a015115a613fa18fbc8dc43ee673ef7b0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD7_3_evidence.svg</t>
+          <t>outputs/figures/FigD7_3_evidence.pdf</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55032</v>
+        <v>54046</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ee6adc7047acd4f464465e023c8bbf792a9336a1f710171596a0e4d8fe40856a</t>
+          <t>99086a3dbe481d6a5b71f04626512c9605e69ecab78130371413f7a8317a2dc5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD7_4_validation.pdf</t>
+          <t>outputs/figures/FigD7_3_evidence.png</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>48000</v>
+        <v>595335</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4a21542da846a97dae48596083568b7709001f9b71e7011787984cd8d3b1ec21</t>
+          <t>7507c754eef39ce1c96afb784a37d58c844b26078acef706bdecf7aad56f5b63</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD7_4_validation.png</t>
+          <t>outputs/figures/FigD7_3_evidence.svg</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>521976</v>
+        <v>52383</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>fa07824828da0bad99cbbea776dd59a96fb3f486e3805046d64cbb97fdcafe80</t>
+          <t>a67694554c53b927e68a088acd97c1a18ff9e0ac7c22f42621750b28f1be48a9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD7_4_validation.svg</t>
+          <t>outputs/figures/FigD7_3_evidence.tiff</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>41913</v>
+        <v>1289062</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>7d0ae9c723b16a530e7fc878a0c6b690c1fc620397996152bff9c5f032a28832</t>
+          <t>69331122bd027fd523493fc5a2fd7e5b524ad87963514787a37250ea11d4735d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD7_5_governance.pdf</t>
+          <t>outputs/figures/FigD7_4_validation.pdf</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>52504</v>
+        <v>53521</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>08f6f69ee37df189f2200059b0927e8c09e32dbfd789436c3bfff370febc6e32</t>
+          <t>5e5f64c034ddfe8271003b0590f9da48648110e094e4c6cee27fc363e0d2a3ef</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD7_5_governance.png</t>
+          <t>outputs/figures/FigD7_4_validation.png</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>520537</v>
+        <v>471042</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>f972c07dbc579296ad8a1c8faaadf0c67943bb380e333121fab6f37b61c66031</t>
+          <t>8f10fe158f6cd498110b4c737a70887913c8e64f93d6cb294ee171f44c5f117c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD7_5_governance.svg</t>
+          <t>outputs/figures/FigD7_4_validation.svg</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45570</v>
+        <v>45044</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>cfd99844a2db4600ea81cf29216573b90004f7172ef34dc1c0f1f620807b5146</t>
+          <t>7bb965b089228a9e4050712be175038b1f26004b9d9ceda4e5c239e754c48dff</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>outputs/local/D7_ablation_redundancy.xlsx</t>
+          <t>outputs/figures/FigD7_4_validation.tiff</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9861</v>
+        <v>985686</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>a96ebb1d62b794f709fcb8d8a048711bbf58cb80d202b2f26e46f5a783eab8a4</t>
+          <t>bbd879ad74d9a5a8172f0b578a4cb0aedc7262e4dd299d5bf3d37690c8989576</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>outputs/local/D7_audit_log.xlsx</t>
+          <t>outputs/figures/FigD7_5_governance.pdf</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>84792</v>
+        <v>51533</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0f135dac17109aa947fa780339d01da2bf72f450d246f43bdfd6b8ba5ae5108f</t>
+          <t>e638c86ce4a5e9ea7bc2c40a96d2ada79b5c66d9374182e791908977d68b07db</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>outputs/local/D7_case_study_exports.xlsx</t>
+          <t>outputs/figures/FigD7_5_governance.png</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>44230</v>
+        <v>470003</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3671e79cdc4ed4f640a63b5e65969ff7d7b86037c0c36f4a98615924e2e5eed8</t>
+          <t>262b314c910ea2fdb5ea220cd8880ed324b2594a148643235c064d1b562bf250</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>outputs/local/D7_d6_interface.schema.json</t>
+          <t>outputs/figures/FigD7_5_governance.svg</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>546</v>
+        <v>39607</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>edc1c46088deb146df6c97efa7a124997e08ceeb0179f609e5e6705908349ba1</t>
+          <t>d824042d7f7929fd2841ba2cb1ca259bb374289b7a3770f2865327013d4a4c9f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>outputs/local/D7_edge_profile_summary.xlsx</t>
+          <t>outputs/figures/FigD7_5_governance.tiff</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>30812</v>
+        <v>993666</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0fab41c05d378d234a33f938f8f81748ba24795b12b908c9a8c310206aea5599</t>
+          <t>a8124854db0f374f5388dad55aafb6d19f994ab04184b787c0294735f5455c70</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>outputs/local/D7_event_windows.parquet</t>
+          <t>outputs/local/D7_ablation_redundancy.xlsx</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>70845</v>
+        <v>9861</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>7fc6239ad5b77da66e04d4abcce8a20621fc7ce111915cfb5fe50cfb7de4f830</t>
+          <t>a96ebb1d62b794f709fcb8d8a048711bbf58cb80d202b2f26e46f5a783eab8a4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>outputs/local/D7_event_windows.xlsx</t>
+          <t>outputs/local/D7_audit_log.xlsx</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>126116</v>
+        <v>85126</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0aa4b388d803cb087e7d0bf36829314f997dac14d39f57ab92a0b23362f352d7</t>
+          <t>6996b7b8916d73721583227be6ee6c2c448e44598f7d0082436e918a724fde97</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>outputs/local/D7_main_scores_hourly.parquet</t>
+          <t>outputs/local/D7_case_study_exports.xlsx</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9816871</v>
+        <v>44230</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0f64524fc8b543be2d5da33901c5c7b1e3ca6655841c4489bbebb660481123cf</t>
+          <t>3671e79cdc4ed4f640a63b5e65969ff7d7b86037c0c36f4a98615924e2e5eed8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>outputs/local/D7_main_scores_hourly.xlsx</t>
+          <t>outputs/local/D7_d6_interface.schema.json</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32383539</v>
+        <v>546</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>c1642b17924fb22d3165f17b107f0615a039ce3fda940e4952545eb4013b555c</t>
+          <t>edc1c46088deb146df6c97efa7a124997e08ceeb0179f609e5e6705908349ba1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>outputs/local/D7_mapping_params.xlsx</t>
+          <t>outputs/local/D7_edge_profile_summary.xlsx</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>20273</v>
+        <v>30812</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>46d7355c413cdfb67a494f2fefb51c4f333dbaa5c413a1bc0e2ff802341c0d35</t>
+          <t>0fab41c05d378d234a33f938f8f81748ba24795b12b908c9a8c310206aea5599</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>outputs/local/D7_multiscale_aggregates.xlsx</t>
+          <t>outputs/local/D7_event_windows.parquet</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>929096</v>
+        <v>70845</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1c61b75561978916b83b9ca03f6485e17890d9719f3ad5d8e5bac22b7866266e</t>
+          <t>7fc6239ad5b77da66e04d4abcce8a20621fc7ce111915cfb5fe50cfb7de4f830</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>outputs/local/D7_reference_window_library.parquet</t>
+          <t>outputs/local/D7_event_windows.xlsx</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>63489</v>
+        <v>126116</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>79a8bb6da54a371c394721ec37fe43b47fdcfe603047396fd2a609f76fcf90a2</t>
+          <t>0aa4b388d803cb087e7d0bf36829314f997dac14d39f57ab92a0b23362f352d7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>outputs/local/D7_reference_window_library.xlsx</t>
+          <t>outputs/local/D7_main_scores_hourly.parquet</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>217159</v>
+        <v>9816871</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>5ab6dab08111d83cc882f14cde37e8a44cd4fe791d33d2bdc31149c4b7a5c84e</t>
+          <t>0f64524fc8b543be2d5da33901c5c7b1e3ca6655841c4489bbebb660481123cf</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>outputs/local/D7_regime_state.parquet</t>
+          <t>outputs/local/D7_main_scores_hourly.xlsx</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>30965123</v>
+        <v>32383539</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>4bcc9fc4963a076ac3367f66933906514d3059b9558fe7ecf35112a210b0975b</t>
+          <t>c1642b17924fb22d3165f17b107f0615a039ce3fda940e4952545eb4013b555c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>outputs/local/D7_regime_state.xlsx</t>
+          <t>outputs/local/D7_mapping_params.xlsx</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>86555483</v>
+        <v>20273</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2b6a21f2bcbb3e0bc98224b4a0bef0fd88fa6241bf0076779a2a461514578a39</t>
+          <t>46d7355c413cdfb67a494f2fefb51c4f333dbaa5c413a1bc0e2ff802341c0d35</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>outputs/local/D7_sensor_influence.parquet</t>
+          <t>outputs/local/D7_multiscale_aggregates.xlsx</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5711635</v>
+        <v>929096</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>551b51782ab00fa2a45ce788c736a3a786f5e98bd0decf442386e98c10ceeca8</t>
+          <t>1c61b75561978916b83b9ca03f6485e17890d9719f3ad5d8e5bac22b7866266e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>outputs/local/D7_sensor_influence.xlsx</t>
+          <t>outputs/local/D7_reference_window_library.parquet</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>12919122</v>
+        <v>63489</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>6f0b729daaad6291eb28e16cb5a3cd7bb04359b7133247073d7d2cedb2fae802</t>
+          <t>79a8bb6da54a371c394721ec37fe43b47fdcfe603047396fd2a609f76fcf90a2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>outputs/local/D7_sensor_profile_summary.xlsx</t>
+          <t>outputs/local/D7_reference_window_library.xlsx</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7506</v>
+        <v>217159</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>cc2bf6813e78c833ef9761874514b5bbb77d204df7ebe65ce4fad898cbc22c01</t>
+          <t>5ab6dab08111d83cc882f14cde37e8a44cd4fe791d33d2bdc31149c4b7a5c84e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>outputs/local/D7_spatial_evidence.parquet</t>
+          <t>outputs/local/D7_regime_state.parquet</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6696159</v>
+        <v>30965123</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>b0035a5ff086111cc5d18c78e1ea383a4aa71bb395b4a0487048293dd9b83eb4</t>
+          <t>4bcc9fc4963a076ac3367f66933906514d3059b9558fe7ecf35112a210b0975b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>outputs/local/D7_spatial_evidence.xlsx</t>
+          <t>outputs/local/D7_regime_state.xlsx</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>16026614</v>
+        <v>86555483</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>fcbc3809f84eff23290f3b39ef1bfd7715c352e7f9d8297a8618ac3746c08ec2</t>
+          <t>2b6a21f2bcbb3e0bc98224b4a0bef0fd88fa6241bf0076779a2a461514578a39</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>outputs/local/D7_spatial_templates.template_bundle.json</t>
+          <t>outputs/local/D7_sensor_influence.parquet</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>452892</v>
+        <v>5711635</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>05166df2a55b4827a95a3755df1e38f085f99c80f71d5099f099774d6db2646c</t>
+          <t>551b51782ab00fa2a45ce788c736a3a786f5e98bd0decf442386e98c10ceeca8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>outputs/local/D7_spatial_templates.xlsx</t>
+          <t>outputs/local/D7_sensor_influence.xlsx</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>186908</v>
+        <v>12919122</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>89963486def67ccf2bcf0b43cd3190b24fb1ecdb7fc77940b4f679cafa1e2842</t>
+          <t>6f0b729daaad6291eb28e16cb5a3cd7bb04359b7133247073d7d2cedb2fae802</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>outputs/local/D7_support_assessment.parquet</t>
+          <t>outputs/local/D7_sensor_profile_summary.xlsx</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>28123</v>
+        <v>7506</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>833ffa282f79fca883fa791c7ccd9a8113af3e3237190128d7d8ee8f981fdb9b</t>
+          <t>cc2bf6813e78c833ef9761874514b5bbb77d204df7ebe65ce4fad898cbc22c01</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>outputs/local/D7_support_assessment.xlsx</t>
+          <t>outputs/local/D7_spatial_evidence.parquet</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>17720</v>
+        <v>6696159</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ccceea1092f3c097c044bf903f72e667fec5c14b06ef0a52a827d33e4f2f0d24</t>
+          <t>b0035a5ff086111cc5d18c78e1ea383a4aa71bb395b4a0487048293dd9b83eb4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>outputs/local/D7_topology_drift_alerts.parquet</t>
+          <t>outputs/local/D7_spatial_evidence.xlsx</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10784</v>
+        <v>16026614</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3b6fc36c522d6fa0eeaba6ba5408caa8079958dc899eeaf353cf437163104100</t>
+          <t>fcbc3809f84eff23290f3b39ef1bfd7715c352e7f9d8297a8618ac3746c08ec2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>outputs/local/D7_topology_drift_alerts.xlsx</t>
+          <t>outputs/local/D7_spatial_templates.template_bundle.json</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>9949</v>
+        <v>452892</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>6b4068d8791367701a84a8befe574e597e7e5c9ad33c108c23c894537e5f4334</t>
+          <t>05166df2a55b4827a95a3755df1e38f085f99c80f71d5099f099774d6db2646c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>outputs/local/D7_topology_registry.json</t>
+          <t>outputs/local/D7_spatial_templates.xlsx</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10933</v>
+        <v>186908</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>f85b868e9941538c8da10ae2dbd4f0c0aa4a9f2f784656a1c9fd925ca2a40d08</t>
+          <t>89963486def67ccf2bcf0b43cd3190b24fb1ecdb7fc77940b4f679cafa1e2842</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>outputs/local/D7_topology_registry.schema.json</t>
+          <t>outputs/local/D7_support_assessment.parquet</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>715</v>
+        <v>28123</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>126497fdca42ce676bedc4f83055a445039233d3f6b8b5d056b06e65eee48e37</t>
+          <t>833ffa282f79fca883fa791c7ccd9a8113af3e3237190128d7d8ee8f981fdb9b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>outputs/local/D7_topology_registry.xlsx</t>
+          <t>outputs/local/D7_support_assessment.xlsx</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>9980</v>
+        <v>17720</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>d287e3075a0d9258964a343239adc2b3df2b3eb27579abdba1a86f80a20ebd8a</t>
+          <t>ccceea1092f3c097c044bf903f72e667fec5c14b06ef0a52a827d33e4f2f0d24</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>outputs/local/D7_topology_registry.yaml</t>
+          <t>outputs/local/D7_topology_drift_alerts.parquet</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2508</v>
+        <v>10784</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>5855cf2bb6d4f570d9d469ee541107ff429951b08067298e78fb1a0f7296c8d0</t>
+          <t>3b6fc36c522d6fa0eeaba6ba5408caa8079958dc899eeaf353cf437163104100</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>outputs/local/D7_validation_results.xlsx</t>
+          <t>outputs/local/D7_topology_drift_alerts.xlsx</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>30224</v>
+        <v>9949</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>31db2243406ef1166aee95f61af52402025d51ef5c1136b9f38d98e68f74dd1b</t>
+          <t>6b4068d8791367701a84a8befe574e597e7e5c9ad33c108c23c894537e5f4334</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>outputs/local/D7_zone_consensus.parquet</t>
+          <t>outputs/local/D7_topology_registry.json</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1208845</v>
+        <v>10933</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>74f38faeaf6b9dd523e4f1196ec07221ad359167e0f8dd6348696aac3ae64127</t>
+          <t>f85b868e9941538c8da10ae2dbd4f0c0aa4a9f2f784656a1c9fd925ca2a40d08</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>outputs/local/D7_zone_consensus.xlsx</t>
+          <t>outputs/local/D7_topology_registry.schema.json</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4773714</v>
+        <v>715</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>87f355c32b07e5cfb17dcbd9604b9aad3f2b98a2708dbc05132d171b6f17f6c5</t>
+          <t>126497fdca42ce676bedc4f83055a445039233d3f6b8b5d056b06e65eee48e37</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>outputs/plot_data/D7_plot_data.csv</t>
+          <t>outputs/local/D7_topology_registry.xlsx</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>5165042</v>
+        <v>9980</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>9cf0b67991f5d9d0aa07c005f1ae20e2d29f9bc7003918cb82874aed80d00885</t>
+          <t>d287e3075a0d9258964a343239adc2b3df2b3eb27579abdba1a86f80a20ebd8a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>outputs/plot_data/D7_plot_data.parquet</t>
+          <t>outputs/local/D7_topology_registry.yaml</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>180365</v>
+        <v>2508</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>07c67efc62194833637deea96361abe3a4905f17786446eeaffb1fbc60d703a3</t>
+          <t>5855cf2bb6d4f570d9d469ee541107ff429951b08067298e78fb1a0f7296c8d0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>outputs/plot_data/D7_plot_data_manifest.json</t>
+          <t>outputs/local/D7_validation_results.xlsx</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>519</v>
+        <v>30224</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>41e144f18ead76df5b4a82453258b04985950e871e4bf2553a18f41cc70b2632</t>
+          <t>31db2243406ef1166aee95f61af52402025d51ef5c1136b9f38d98e68f74dd1b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>outputs/reports/D7_EXPERT_REPORT_v2.1.docx</t>
+          <t>outputs/local/D7_zone_consensus.parquet</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1930105</v>
+        <v>1208845</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>de5bff6d2b0b19d12b5b87eb0d11bb4e7da1bf313af43764faeaa5e7e80a5f50</t>
+          <t>74f38faeaf6b9dd523e4f1196ec07221ad359167e0f8dd6348696aac3ae64127</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>outputs/reports/D7_EXPERT_REPORT_v2.1.md</t>
+          <t>outputs/local/D7_zone_consensus.xlsx</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>6008</v>
+        <v>4773714</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>7b33f201e4a4024c5f46152da4b0eeb0eb150f15f396087a3eacf4735d7173af</t>
+          <t>87f355c32b07e5cfb17dcbd9604b9aad3f2b98a2708dbc05132d171b6f17f6c5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>outputs/reports/D7_FIGURE_CAPTIONS_v2.1.md</t>
+          <t>outputs/plot_data/D7_plot_data.csv</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2022</v>
+        <v>27713153</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>79c715bb3df74ec90b1816f911bf2a88f36fa7ad71e4f6262b6d3df8b470469e</t>
+          <t>ee688d5969652f0a4d9a045229bf4fa7e4d92694b7630f31437e4fc55faab97b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>outputs/reports/D7_PROJECT_DIRECTORY_GUIDE_v2.1.docx</t>
+          <t>outputs/plot_data/D7_plot_data.parquet</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>40298</v>
+        <v>896956</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2cce4bf06a2f8825476b1c551a897e1047e1f5a67e354ba330ecaa5f423b92b2</t>
+          <t>9740bc0a48d5679b2e03c791b49e34c0adfce06f85abb252ad26eea128703526</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>outputs/reports/D7_PROJECT_DIRECTORY_GUIDE_v2.1.md</t>
+          <t>outputs/plot_data/D7_plot_data_manifest.json</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4870</v>
+        <v>856</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>269d82cbb7dc64ca7fa0efb8c86535600cf8da72f3aae06aa448794195637a82</t>
+          <t>2da736bd764b8c6ca819aa256a4fa917ff90edccce5d18820ffc6c43d020288c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>outputs/sensitivity/D7_sensitivity_manifest.json</t>
+          <t>outputs/reports/D7_EXPERT_REPORT_v2.1.docx</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1400</v>
+        <v>1994234</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>bd0d7a20ba97af03e87f2c66570ce6fb67b1468394aa3401b9ee8f51c6cea26d</t>
+          <t>53cfd78c1ad0d2946b8e361958747016936cc7ddb38bbf01a840c1f9477e7a99</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>outputs/sensitivity/D7_shadow_scores.parquet</t>
+          <t>outputs/reports/D7_EXPERT_REPORT_v2.1.md</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2966985</v>
+        <v>6202</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>5a20c2b223c25f33756c868fa2eebd0d4f25b0510c46cc99d9612d665abad6b9</t>
+          <t>0e7db5c3ac36ec1b0305bd44d92caaafb0adda60865953bebe24a07944e4273f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>outputs/sensitivity/D7_shadow_scores.xlsx</t>
+          <t>outputs/reports/D7_FIGURE_CAPTIONS_v2.1.md</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>10049007</v>
+        <v>2263</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>eac37ae348e7dbb9c062331975a9631d1c1369a68e7c45f3ef30bed775a59c0c</t>
+          <t>4ae54945b07f517736422b6ecd412dd68085f9b393e064e347e8662d989f8df0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>outputs/sensitivity/D7_shadow_template_shift.xlsx</t>
+          <t>outputs/reports/D7_PROJECT_DIRECTORY_GUIDE_v2.1.docx</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>41716</v>
+        <v>40309</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>6e4f528897face976d57525a071f3c79a9062c1c23d74509d16362948ff5962d</t>
+          <t>83c6b5df38dc0d98ed5b89c96c5d696056887286b5629009b9601b906dcdcc8a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>outputs/sensitivity/D7_track_invariance.xlsx</t>
+          <t>outputs/reports/D7_PROJECT_DIRECTORY_GUIDE_v2.1.md</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>14475</v>
+        <v>4887</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>a0dc72455ca2838b4628b24794b545403d21172f59cb5c277a01127d49383410</t>
+          <t>5add68cc0d5f038586d648929100385fbc0cc70af62fe2fb9e15f6145d01e00b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>outputs/shadow_v2/D7_graph_structure_learning_shadow.parquet</t>
+          <t>outputs/sensitivity/D7_sensitivity_manifest.json</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>9348</v>
+        <v>1400</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>d5c5d09e445021f08ef4bc32d14aef2b7e28fb52ce807395176d750c987ad0da</t>
+          <t>bd0d7a20ba97af03e87f2c66570ce6fb67b1468394aa3401b9ee8f51c6cea26d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>outputs/shadow_v2/D7_graph_structure_learning_shadow.xlsx</t>
+          <t>outputs/sensitivity/D7_shadow_scores.parquet</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>8313</v>
+        <v>2966985</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>5128724d8e273420d1f87f8561bbe4699dd9f949898f51583947b0cf153aff72</t>
+          <t>5a20c2b223c25f33756c868fa2eebd0d4f25b0510c46cc99d9612d665abad6b9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>outputs/sensitivity/D7_shadow_scores.xlsx</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>10049007</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>eac37ae348e7dbb9c062331975a9631d1c1369a68e7c45f3ef30bed775a59c0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>outputs/sensitivity/D7_shadow_template_shift.xlsx</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>41716</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>6e4f528897face976d57525a071f3c79a9062c1c23d74509d16362948ff5962d</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>outputs/sensitivity/D7_track_invariance.xlsx</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>14475</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>a0dc72455ca2838b4628b24794b545403d21172f59cb5c277a01127d49383410</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>outputs/shadow_v2/D7_graph_structure_learning_shadow.parquet</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>9348</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>d5c5d09e445021f08ef4bc32d14aef2b7e28fb52ce807395176d750c987ad0da</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>outputs/shadow_v2/D7_graph_structure_learning_shadow.xlsx</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>8313</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>5128724d8e273420d1f87f8561bbe4699dd9f949898f51583947b0cf153aff72</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>outputs/shadow_v2/D7_shadow_v2_manifest.json</t>
         </is>
       </c>
-      <c r="B67" t="n">
+      <c r="B72" t="n">
         <v>263</v>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>fa05e2d31b9b363ca7ed9b5a4cd6eec8f44388bfbf052225243ddde2329ffeed</t>
         </is>

--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_audit_log.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_audit_log.xlsx
@@ -944,7 +944,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ccfbca5b9dd57957714bded6fc9e99e6d502b16e91c7896ad0347d8f3658f0f3</t>
+          <t>c92691d09c8deddf3657ef19e4277dde9da33360004b4c7f89dff5297a41448f</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>a12d21fd62dd04f5d6dcd660f41bde69f941e4f4a9ccf1cda2e1623d61089a32</t>
+          <t>03ae1c18875a33d03f88e9cfe97858065bd07d68bda4bdfde2fd69307a5c0a92</t>
         </is>
       </c>
     </row>
@@ -1030,11 +1030,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>63355</v>
+        <v>63169</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14290cb202b7cfe5dcdca221de89023aabd324fded52f87c207f9173df0784ba</t>
+          <t>600293b719f0a5b1485fc0c89f76b10ce921bece0ac37398515f70b6ac31aecf</t>
         </is>
       </c>
     </row>
@@ -1045,11 +1045,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>385799</v>
+        <v>384819</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>055f03c1decf7348eb20b879356faaadb23329fe9a86f9f1803d8ff3444a4b88</t>
+          <t>7913a3fe1686e1136aa2d2deaa65649217622f377dbc3a1f47d74d0f9c8bc8d9</t>
         </is>
       </c>
     </row>
@@ -1060,11 +1060,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69127</v>
+        <v>65364</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>7cdf92f33c51439e135456d40a72a2da7dd470ec6d5b25c5e97cca5db13c0915</t>
+          <t>adc3a2ec9c781e2b665190d3c117c564c6dc885ff0365e395a74dfa42bc1ef7f</t>
         </is>
       </c>
     </row>
@@ -1075,11 +1075,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7350736</v>
+        <v>7351238</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>35c45a2caff1b1f979ff182f6e44550a015115a613fa18fbc8dc43ee673ef7b0</t>
+          <t>7c5fceec041a4f4d32d5dd54495248b5982c7eaa3c6099f6f86048c9c8d10f82</t>
         </is>
       </c>
     </row>
@@ -1285,11 +1285,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>85126</v>
+        <v>85117</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6996b7b8916d73721583227be6ee6c2c448e44598f7d0082436e918a724fde97</t>
+          <t>b676e4cb2f4f0f6fc5ebbc73787305f7b5beb3121547a89d057d1aaf41758b88</t>
         </is>
       </c>
     </row>
@@ -1810,11 +1810,11 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1994234</v>
+        <v>1992957</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>53cfd78c1ad0d2946b8e361958747016936cc7ddb38bbf01a840c1f9477e7a99</t>
+          <t>ea11e3ada916315ff77216fda15c41b1ae7a9e28164122ca70ce2ce74d7760a1</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>0e7db5c3ac36ec1b0305bd44d92caaafb0adda60865953bebe24a07944e4273f</t>
+          <t>78680b1c183f0ea61d4715b9ecd7f98962e154d6bc8ba9595165f07fa15e10fd</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>83c6b5df38dc0d98ed5b89c96c5d696056887286b5629009b9601b906dcdcc8a</t>
+          <t>ce9bb9d4e988b8441420bb1da589e5c35a78bc154dfcd4ad7981a8d0987856b9</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>5add68cc0d5f038586d648929100385fbc0cc70af62fe2fb9e15f6145d01e00b</t>
+          <t>034547f8813a00d410b11d12a37133812ae541138500c7e0bd68d32779d09059</t>
         </is>
       </c>
     </row>

--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_audit_log.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_audit_log.xlsx
@@ -944,7 +944,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8ba0309e3568e5c4860a71fb4789cd621cc704b6366b86bd23bd8727b87cc84e</t>
+          <t>fa2466861d8a922e178b21cb7dc48ceae389d113a47cb70ecf6f78e4054e558e</t>
         </is>
       </c>
     </row>
@@ -955,11 +955,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>89d5b54cdb4b970d95acb829f7ddf6eb230b270d6000dd8c87047f29c6f1c3d4</t>
+          <t>6b2be960239cd2ceeb34404018114a5c17f59a578dad2405a13407a8eff6fbe4</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>309e462028bd4b6ff796d4c6627f36a4e82d665afe6c29d07dfd70f5866257a1</t>
+          <t>ec761c6a520f2fe7877ee0c0923033444c3a7d306b21610db1147dbfa297d5a8</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bc3f147b7b79ae412151717ff8450396368a89451ae38599788c12fb1ff8d96f</t>
+          <t>28bdc0e5e549b2bc692e32c8d0ddd1de5bcdfbe966c0ebb5f93623dec3925e45</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0730bb25fb25f32f10f8ca24bbe9ffcb7268dc65daced0447ad91b523fe874b6</t>
+          <t>a829d5a7a81ec5c7f18b4995e4a51ca96bf3b08e4780f00e5f5e555b121c82dd</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>d3ad18ca714624bfc20b20ca22f7c5933af77ffa342eb789474953970cd7246d</t>
+          <t>129d119a8a96f2eb3f12c19bce273f0e89de5336053f8e89a531b51f6e05b9ae</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8a9e29f8a55d2c569e2767104100b48bdffd8ac81de2b8012206269c19da90ce</t>
+          <t>95945989fd64a037ba7d895f5d161640ff3db2ed1f4b0f49b1e728abfc55ef86</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ee6adc7047acd4f464465e023c8bbf792a9336a1f710171596a0e4d8fe40856a</t>
+          <t>40f5f206a96b2a1ab537431d7402cfde549404c3fefd7874711e993ab2f57633</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4a21542da846a97dae48596083568b7709001f9b71e7011787984cd8d3b1ec21</t>
+          <t>6dc59f9a66722ba8511c03c1505b11594eedb05d44ba8635384cef9d3bf33eb1</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>fa07824828da0bad99cbbea776dd59a96fb3f486e3805046d64cbb97fdcafe80</t>
+          <t>a6a8d8b9b82be28cc4f0ee3e5ae4d7755f19589992e6025daccd79ec0722c367</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>7d0ae9c723b16a530e7fc878a0c6b690c1fc620397996152bff9c5f032a28832</t>
+          <t>8e30293771ab6308eb70bbb62c4fd6ffbff6f88cf89fd9e4d11c55dcedfa6f28</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>08f6f69ee37df189f2200059b0927e8c09e32dbfd789436c3bfff370febc6e32</t>
+          <t>5d498bc77567ab27c4b2420739ee34c45dd05c7b0927908c49d9cfb456806624</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>cfd99844a2db4600ea81cf29216573b90004f7172ef34dc1c0f1f620807b5146</t>
+          <t>2fee1e0187b6fd2127fbbbf224315ff95bbec2b9a5477ea73f205eca8f30c4fd</t>
         </is>
       </c>
     </row>
@@ -1195,11 +1195,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9861</v>
+        <v>9864</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>a96ebb1d62b794f709fcb8d8a048711bbf58cb80d202b2f26e46f5a783eab8a4</t>
+          <t>69afbeef7961bb539c37dbbf0dd441b7cb8ccfdb0efedbf48037d706fa216348</t>
         </is>
       </c>
     </row>
@@ -1210,11 +1210,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>84792</v>
+        <v>84796</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0f135dac17109aa947fa780339d01da2bf72f450d246f43bdfd6b8ba5ae5108f</t>
+          <t>2475d445af3100eb38803cb3b6c2c9fc985305d326e805855a7ad9d501704261</t>
         </is>
       </c>
     </row>
@@ -1645,11 +1645,11 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>30224</v>
+        <v>30225</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>31db2243406ef1166aee95f61af52402025d51ef5c1136b9f38d98e68f74dd1b</t>
+          <t>84c3c35a3b4dc52e44bae38d481696fa84e82703c67b85c93640de122ee489f0</t>
         </is>
       </c>
     </row>
@@ -1690,11 +1690,11 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>5165042</v>
+        <v>5165043</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>9cf0b67991f5d9d0aa07c005f1ae20e2d29f9bc7003918cb82874aed80d00885</t>
+          <t>1f75dcfe75ea181d44756205c4c67c884b703df10e19a39baccc3a9b747c0e10</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>07c67efc62194833637deea96361abe3a4905f17786446eeaffb1fbc60d703a3</t>
+          <t>384394c9daba8b84d7f72367f40b787581f979cc09602467d5c40a656f2f57f7</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>41e144f18ead76df5b4a82453258b04985950e871e4bf2553a18f41cc70b2632</t>
+          <t>8de67af78c2349fbef13626971e08bb6590b6e740ef3749c4f0845105762681b</t>
         </is>
       </c>
     </row>
@@ -1735,11 +1735,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1930105</v>
+        <v>1930182</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>de5bff6d2b0b19d12b5b87eb0d11bb4e7da1bf313af43764faeaa5e7e80a5f50</t>
+          <t>c84540388eff3016e62277d76059e4c96705ff51031c2a23eb03a8fb16a41a50</t>
         </is>
       </c>
     </row>
@@ -1750,11 +1750,11 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>6008</v>
+        <v>6256</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>7b33f201e4a4024c5f46152da4b0eeb0eb150f15f396087a3eacf4735d7173af</t>
+          <t>75e15bb2ed88eac6aeffc2dff86d965618f949db99953d5761c5cce2a0b1d7c5</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2cce4bf06a2f8825476b1c551a897e1047e1f5a67e354ba330ecaa5f423b92b2</t>
+          <t>226969ec049043feb6d61d789e6ea4e2aece4e759f46c95f10859a22735937d8</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>269d82cbb7dc64ca7fa0efb8c86535600cf8da72f3aae06aa448794195637a82</t>
+          <t>acbbbce207ca2b2e0291df73d164beb921480aa2585c506e2632c07dc711dcc5</t>
         </is>
       </c>
     </row>
@@ -1810,11 +1810,11 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1400</v>
+        <v>2294</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>bd0d7a20ba97af03e87f2c66570ce6fb67b1468394aa3401b9ee8f51c6cea26d</t>
+          <t>11779195ba6911be55e9a1c22ba203526fa59d5afc4aaab377e4496f842d9d9d</t>
         </is>
       </c>
     </row>
@@ -1825,11 +1825,11 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2966985</v>
+        <v>2973499</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>5a20c2b223c25f33756c868fa2eebd0d4f25b0510c46cc99d9612d665abad6b9</t>
+          <t>3f38d8437d14ae8e8fb4210d8089cc415d10e66b0decee393e2ba006b38426a3</t>
         </is>
       </c>
     </row>
@@ -1840,11 +1840,11 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>10049007</v>
+        <v>10056157</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>eac37ae348e7dbb9c062331975a9631d1c1369a68e7c45f3ef30bed775a59c0c</t>
+          <t>e9d7baa44d45dee99f774e430831499b9112848152a8cbbbacbb41396ab75d22</t>
         </is>
       </c>
     </row>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>41716</v>
+        <v>41828</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>6e4f528897face976d57525a071f3c79a9062c1c23d74509d16362948ff5962d</t>
+          <t>d59e19250c9a8fef78e39781d7ced325877570437e4a48fd7937f8a9f14d0a0d</t>
         </is>
       </c>
     </row>
@@ -1870,11 +1870,11 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>14475</v>
+        <v>14483</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>a0dc72455ca2838b4628b24794b545403d21172f59cb5c277a01127d49383410</t>
+          <t>54a33f642a94acd7bf5eca2f165f91be6b41682358d3a7120847e1e01c7bf04f</t>
         </is>
       </c>
     </row>

--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_audit_log.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_audit_log.xlsx
@@ -944,7 +944,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fa2466861d8a922e178b21cb7dc48ceae389d113a47cb70ecf6f78e4054e558e</t>
+          <t>bd4643d83c7adc995f443d166b7049c389811d775b9dd23f2f021e9156372353</t>
         </is>
       </c>
     </row>
@@ -955,11 +955,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2381</v>
+        <v>2382</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6b2be960239cd2ceeb34404018114a5c17f59a578dad2405a13407a8eff6fbe4</t>
+          <t>e6a4df553688a6a6c3c62afe49e80e7b4d56575913e55f548409ea06f11d3f3f</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ec761c6a520f2fe7877ee0c0923033444c3a7d306b21610db1147dbfa297d5a8</t>
+          <t>d9a32f4c45fbc37a977d3aa6471439958b9b96dfda833847f6f873654a442521</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>28bdc0e5e549b2bc692e32c8d0ddd1de5bcdfbe966c0ebb5f93623dec3925e45</t>
+          <t>3ea5adbd3e99d038c5cee9205769a9667889db607329b3d207474ca7118ebc7f</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>a829d5a7a81ec5c7f18b4995e4a51ca96bf3b08e4780f00e5f5e555b121c82dd</t>
+          <t>0c2c1f35a5c2aae8806f5e894ae7b33195c9c97a3e6e50597f0a8f67488022f0</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>129d119a8a96f2eb3f12c19bce273f0e89de5336053f8e89a531b51f6e05b9ae</t>
+          <t>a21ef5ec5f69fa2830f6e45398d60123a35d67350d1e7913dafe545b8f5e6cbf</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>95945989fd64a037ba7d895f5d161640ff3db2ed1f4b0f49b1e728abfc55ef86</t>
+          <t>9b44a8dbc11b1371807476058aa01ac19a0a5707ea82a93850dbaee3a128b2c9</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>40f5f206a96b2a1ab537431d7402cfde549404c3fefd7874711e993ab2f57633</t>
+          <t>0c79b045fb3e9bde63aa590ad4377075ccbe97f8bd9ffd722f39d79d0b479c6b</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6dc59f9a66722ba8511c03c1505b11594eedb05d44ba8635384cef9d3bf33eb1</t>
+          <t>c0edba708a32383e91befd4c55813fba4e2dc4cdbbf4638a4ecd69dfdd7ab40d</t>
         </is>
       </c>
     </row>
@@ -1120,11 +1120,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>521976</v>
+        <v>521995</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>a6a8d8b9b82be28cc4f0ee3e5ae4d7755f19589992e6025daccd79ec0722c367</t>
+          <t>c3488d51590533f604b71ee41918987c7c7c07604fbf190bec3c653c394db6f4</t>
         </is>
       </c>
     </row>
@@ -1135,11 +1135,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>41913</v>
+        <v>41915</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>8e30293771ab6308eb70bbb62c4fd6ffbff6f88cf89fd9e4d11c55dcedfa6f28</t>
+          <t>9ef811e36163ea2f00a4eee6fa97549d7cd0c11eddce9ca88f4a6b3b133ed693</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5d498bc77567ab27c4b2420739ee34c45dd05c7b0927908c49d9cfb456806624</t>
+          <t>da194e7c341735eec0b37c10ede80e76ec1e23af4e651b986987d1e7a13b3780</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2fee1e0187b6fd2127fbbbf224315ff95bbec2b9a5477ea73f205eca8f30c4fd</t>
+          <t>57538fa17db33a2cddc13bc5a9f910b1673f3181ce33919ca2d8a66ae38317af</t>
         </is>
       </c>
     </row>
@@ -1195,11 +1195,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9864</v>
+        <v>9871</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>69afbeef7961bb539c37dbbf0dd441b7cb8ccfdb0efedbf48037d706fa216348</t>
+          <t>08b4536fdb8c8c7764454a75baf7dc7289feacea022e4849ff8cb79598594701</t>
         </is>
       </c>
     </row>
@@ -1210,11 +1210,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>84796</v>
+        <v>84790</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2475d445af3100eb38803cb3b6c2c9fc985305d326e805855a7ad9d501704261</t>
+          <t>1fb2c61017f90a2638871ce56ba7ba51ff8787abf224529202e0345b11336222</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>84c3c35a3b4dc52e44bae38d481696fa84e82703c67b85c93640de122ee489f0</t>
+          <t>52fd7857243deb4d1dad24ad45fb5c543db60759e769595e73f11d5b03d56db2</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1f75dcfe75ea181d44756205c4c67c884b703df10e19a39baccc3a9b747c0e10</t>
+          <t>1222ce6fb9af8e7b25ac656042a3127b963182bce77172d2c0595ff885ba5ecb</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>384394c9daba8b84d7f72367f40b787581f979cc09602467d5c40a656f2f57f7</t>
+          <t>805142eb1fe1ced95bd7a2ae0152db33f430f5bc7e27b89c5d78c3756a689423</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>8de67af78c2349fbef13626971e08bb6590b6e740ef3749c4f0845105762681b</t>
+          <t>e430b9fc14647fcde8cc678f4e1a717332067b9da905c812c18a8564a6487331</t>
         </is>
       </c>
     </row>
@@ -1735,11 +1735,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1930182</v>
+        <v>1930403</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>c84540388eff3016e62277d76059e4c96705ff51031c2a23eb03a8fb16a41a50</t>
+          <t>7b651b6a32b488944c03d88f9337cf71b23da393c88a754a92cf85776f14fdc7</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>75e15bb2ed88eac6aeffc2dff86d965618f949db99953d5761c5cce2a0b1d7c5</t>
+          <t>2b775653078029d73f8840a9bfe7e0d3a3caaecb73d29126895f29c7b7c72c92</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>226969ec049043feb6d61d789e6ea4e2aece4e759f46c95f10859a22735937d8</t>
+          <t>4faec9949a0a16273d5fa79fa8b754ffa5e679fb0037c62dbdee9bdf738eca89</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>acbbbce207ca2b2e0291df73d164beb921480aa2585c506e2632c07dc711dcc5</t>
+          <t>ca6459008e52356823b4fe8325128ec91f1c3a363e95565bdc30674acb299b2d</t>
         </is>
       </c>
     </row>
@@ -1810,11 +1810,11 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2294</v>
+        <v>2296</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>11779195ba6911be55e9a1c22ba203526fa59d5afc4aaab377e4496f842d9d9d</t>
+          <t>846af89e9545f03a184dbc778eeec2dd0e6044ee86500c1f2ab45f2ae4a9153a</t>
         </is>
       </c>
     </row>
@@ -1825,11 +1825,11 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2973499</v>
+        <v>2993805</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>3f38d8437d14ae8e8fb4210d8089cc415d10e66b0decee393e2ba006b38426a3</t>
+          <t>9e7d5b249f60bdf3f3d43710b2b18f4efcd67f106e71e2ab87905198ad51a4c5</t>
         </is>
       </c>
     </row>
@@ -1840,11 +1840,11 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>10056157</v>
+        <v>10027466</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>e9d7baa44d45dee99f774e430831499b9112848152a8cbbbacbb41396ab75d22</t>
+          <t>5a4ce1d9a80826f737f74bc4a120989d7a6aae4350a13ed7a60488dda5476cdd</t>
         </is>
       </c>
     </row>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>41828</v>
+        <v>41664</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>d59e19250c9a8fef78e39781d7ced325877570437e4a48fd7937f8a9f14d0a0d</t>
+          <t>883f85352affa092b4d7363c17932141eddb2d4125f2d8524ee6d064c72d16e9</t>
         </is>
       </c>
     </row>
@@ -1870,11 +1870,11 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>14483</v>
+        <v>14391</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>54a33f642a94acd7bf5eca2f165f91be6b41682358d3a7120847e1e01c7bf04f</t>
+          <t>65353706c72c28ac303edc80198112ac05417054df4da0cbad72c9ff1525e37f</t>
         </is>
       </c>
     </row>

--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_audit_log.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_audit_log.xlsx
@@ -944,7 +944,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bd4643d83c7adc995f443d166b7049c389811d775b9dd23f2f021e9156372353</t>
+          <t>c093078b779e0f2570dfc7e8d69c46e6b1be4194f02f377f88f332b781db3709</t>
         </is>
       </c>
     </row>
@@ -955,11 +955,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>e6a4df553688a6a6c3c62afe49e80e7b4d56575913e55f548409ea06f11d3f3f</t>
+          <t>25007a8e5c437cf6a1ce97dbc5d58b42add2d71190e937cde29df3cfa3c6dc77</t>
         </is>
       </c>
     </row>
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>49208</v>
+        <v>49360</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>d9a32f4c45fbc37a977d3aa6471439958b9b96dfda833847f6f873654a442521</t>
+          <t>28d38d009df41c8b295fa74488fd90290a095f5b8d2494def28224171304fa6f</t>
         </is>
       </c>
     </row>
@@ -985,11 +985,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>282038</v>
+        <v>276723</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3d4abf7093191a47db0e323225200ccf9f03106afb818dade304137401ebb469</t>
+          <t>b6b62dafe200e9be8de90d6f916cb70e0659ec43063979047b38d935558f35f5</t>
         </is>
       </c>
     </row>
@@ -1000,11 +1000,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37998</v>
+        <v>38538</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3ea5adbd3e99d038c5cee9205769a9667889db607329b3d207474ca7118ebc7f</t>
+          <t>4bdfb2b07797bd1c80841e2a6dc8009e41b8a2e8687905dd1e36512eaa745bfd</t>
         </is>
       </c>
     </row>
@@ -1015,11 +1015,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>68792</v>
+        <v>57645</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0c2c1f35a5c2aae8806f5e894ae7b33195c9c97a3e6e50597f0a8f67488022f0</t>
+          <t>1e59e451fd53c72ee0cf850fdcca5ce1b4cca0775b44ec2a86caf6a31c5e7e15</t>
         </is>
       </c>
     </row>
@@ -1030,11 +1030,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>345707</v>
+        <v>346048</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>54df2039c1f7089650f77d0290fc425757a27b3fca852bcf4a65fa8e44837889</t>
+          <t>65a074c6f602540b91350b99267fee96161df51cc2475fbcc22cbdb337c294e7</t>
         </is>
       </c>
     </row>
@@ -1045,11 +1045,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70324</v>
+        <v>60008</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>a21ef5ec5f69fa2830f6e45398d60123a35d67350d1e7913dafe545b8f5e6cbf</t>
+          <t>bc3c07ad98e4a7889603e632bec35a61cba6a559054e821c98d70caf09fd06df</t>
         </is>
       </c>
     </row>
@@ -1060,11 +1060,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54403</v>
+        <v>54621</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9b44a8dbc11b1371807476058aa01ac19a0a5707ea82a93850dbaee3a128b2c9</t>
+          <t>16bc271e20fd4361223d7677b458c909dc551003a39cf1bf7b9680eeed386820</t>
         </is>
       </c>
     </row>
@@ -1075,11 +1075,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>573661</v>
+        <v>570148</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>a2db09eaeb1480d9fb757d780c4447c44585ec534a7eba04524acd5167011179</t>
+          <t>946e17bebc7716f5dce800e2d8bca417537abd98e3bc0adb1a8571359e6e6e78</t>
         </is>
       </c>
     </row>
@@ -1090,11 +1090,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55032</v>
+        <v>55621</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0c79b045fb3e9bde63aa590ad4377075ccbe97f8bd9ffd722f39d79d0b479c6b</t>
+          <t>b427b0cad92c5239a18e979ccc97ec47827f9ad71ffedff8c2bf13c2173d0b36</t>
         </is>
       </c>
     </row>
@@ -1105,11 +1105,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>48000</v>
+        <v>48157</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>c0edba708a32383e91befd4c55813fba4e2dc4cdbbf4638a4ecd69dfdd7ab40d</t>
+          <t>3cd5b44f2c719147a43d19656eea0145f85a3db14a0f29038e0938b546594977</t>
         </is>
       </c>
     </row>
@@ -1120,11 +1120,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>521995</v>
+        <v>520891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>c3488d51590533f604b71ee41918987c7c7c07604fbf190bec3c653c394db6f4</t>
+          <t>2dc5dd1210cf7323017af5b8f3469aa1e26420a21a8405830c7111673a9be0de</t>
         </is>
       </c>
     </row>
@@ -1135,11 +1135,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>41915</v>
+        <v>42706</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9ef811e36163ea2f00a4eee6fa97549d7cd0c11eddce9ca88f4a6b3b133ed693</t>
+          <t>a2a5f071d9ec7a8f2b91160fef3e7dc5d4d65f6b1ddb11973df353896ea1ef82</t>
         </is>
       </c>
     </row>
@@ -1150,11 +1150,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>52504</v>
+        <v>52659</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>da194e7c341735eec0b37c10ede80e76ec1e23af4e651b986987d1e7a13b3780</t>
+          <t>deac4d89588b01514d6d3d3d50717962c352999b89ca59804211b868ae3c8ac4</t>
         </is>
       </c>
     </row>
@@ -1165,11 +1165,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>520537</v>
+        <v>520538</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>f972c07dbc579296ad8a1c8faaadf0c67943bb380e333121fab6f37b61c66031</t>
+          <t>28ab27d4343f0f6a158a360d1ceaffac4110e26d5a15771fd99492ee1f7b3498</t>
         </is>
       </c>
     </row>
@@ -1180,11 +1180,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45570</v>
+        <v>46326</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>57538fa17db33a2cddc13bc5a9f910b1673f3181ce33919ca2d8a66ae38317af</t>
+          <t>d1a3a5b253c49e00fac97d632590e3a49477f05db294a0fea39fe5670c428352</t>
         </is>
       </c>
     </row>
@@ -1210,11 +1210,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>84790</v>
+        <v>84791</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1fb2c61017f90a2638871ce56ba7ba51ff8787abf224529202e0345b11336222</t>
+          <t>ca5d2c91ea2f9072d9829c85534dfc0ea59ac0d88ee962a7c6b7d1c85f9867ab</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1222ce6fb9af8e7b25ac656042a3127b963182bce77172d2c0595ff885ba5ecb</t>
+          <t>f03c0ba2b0ccab34bbfb00340bba874b567eb31f98f07157aa77c04badae2db1</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>805142eb1fe1ced95bd7a2ae0152db33f430f5bc7e27b89c5d78c3756a689423</t>
+          <t>df5e7d013ecf2249fac140c6cd0ab98258ffe5e4897e0823e343f8834f6807ad</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>e430b9fc14647fcde8cc678f4e1a717332067b9da905c812c18a8564a6487331</t>
+          <t>57615be96f0bd1edd80accf81cdc638668eabe5ccd9adf59311b849a73191ccc</t>
         </is>
       </c>
     </row>

--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_audit_log.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_audit_log.xlsx
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -519,11 +519,11 @@
         <v>529</v>
       </c>
       <c r="H2" t="n">
-        <v>128.0534333999967</v>
+        <v>147.5516602999996</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>d7-v2.2.0-20260726</t>
+          <t>d7-v2.3.0-20260726</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,7 +636,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>orp_validation_graded_diagonal_model</t>
+          <t>family_support_requires_node_validation</t>
         </is>
       </c>
       <c r="B7" t="b">
@@ -644,14 +644,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>model complexity and evidence maturity are separated</t>
+          <t>family evidence is shared once; node validation limits final L3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>validation_nonlocalization_gates</t>
+          <t>dual_interface_contract</t>
         </is>
       </c>
       <c r="B8" t="b">
@@ -659,14 +659,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>detection, negative controls and chatter</t>
+          <t>sensor-hour score report and pair-hour decision gate are separate</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>top1_claim_specific_gate</t>
+          <t>process_guard_is_not_veto</t>
         </is>
       </c>
       <c r="B9" t="b">
@@ -674,14 +674,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.70 observed versus 0.80 target; only node-specific Veto is affected</t>
+          <t>process coherence suppresses attribution only</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>track_invariance</t>
+          <t>orp_validation_graded_diagonal_model</t>
         </is>
       </c>
       <c r="B10" t="b">
@@ -689,20 +689,65 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IE_track, event Jaccard and culprit rho</t>
+          <t>model complexity and evidence maturity are separated</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>validation_nonlocalization_gates</t>
+        </is>
+      </c>
+      <c r="B11" t="b">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>detection, negative controls and chatter</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>top1_claim_specific_gate</t>
+        </is>
+      </c>
+      <c r="B12" t="b">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0.70 observed versus 0.80 target; only node-specific Veto is affected</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>track_invariance</t>
+        </is>
+      </c>
+      <c r="B13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>IE_track, event Jaccard and culprit rho</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>figure_qa</t>
         </is>
       </c>
-      <c r="B11" t="b">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B14" t="b">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>SVG/PDF/600dpi PNG/TIFF and frozen plot data</t>
         </is>
@@ -1059,7 +1104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C81"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1086,11 +1131,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16597</v>
+        <v>19105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7df5e0e691cffad772a973cbf58f1bfea09ab69e23d7b14138e6c8bd2bd80b59</t>
+          <t>804524f154db10052088cbefd6e40182dd66dacb1101834812f93890c9bd3024</t>
         </is>
       </c>
     </row>
@@ -1101,11 +1146,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2837</v>
+        <v>2839</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>e82766fcff5dfa31d2d37d55f961058f936971ddb6f2a8d88209aae21f53fda9</t>
+          <t>e1400ad8d5c7256166dd4df1701bf3947eec5d097b55cb839db584c09e4066cb</t>
         </is>
       </c>
     </row>
@@ -1116,11 +1161,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>51678</v>
+        <v>51075</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>89948bd0c50e2debca59fd12237d90ad0bd54dce2a69384eaa9d7ac400ba673f</t>
+          <t>4f70ea737d21115d304e04ab89837515394e3658d18853e8f9ccecfb03e0ad04</t>
         </is>
       </c>
     </row>
@@ -1131,11 +1176,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>403549</v>
+        <v>401463</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0ef33d438a4ea1f4c82022a9a99cf3a9086a216ba4275d39523da56547a3a3d0</t>
+          <t>64cade07a37d7aed989a19c859d5315b158dd125adbbaa2e2573855a59d082e0</t>
         </is>
       </c>
     </row>
@@ -1146,11 +1191,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44173</v>
+        <v>44204</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5efbe995b0436b202f8b0cbd90b0a88444536a5efe383dbb0bc03ad4a6e6f74a</t>
+          <t>d04feb1d398a2ee13349dfc382c3a53275489e89708b4607b165367f0e825bbb</t>
         </is>
       </c>
     </row>
@@ -1161,11 +1206,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>993728</v>
+        <v>982298</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1d151d525d5630b76577836ae381b413b959d93a464d42dbd0be786d5c5a1be8</t>
+          <t>e202b1a1dc9ac46e875f75029ac3dd74426b36147d8c58b9026d92a0b3d03d69</t>
         </is>
       </c>
     </row>
@@ -1176,11 +1221,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>57636</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>65d478058b628272e75fbcd9a7b0c851668bac5de59394d588136dd0e0542008</t>
+          <t>d1c2430efd545f1fabfc6d8718acfc0f2ff92c2bf653da270cba24dd9d8684d7</t>
         </is>
       </c>
     </row>
@@ -1191,11 +1236,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>341102</v>
+        <v>341105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>99a805a70243a3850743ac328b8c78ae6bc119c3ef40219ab5c57645e09e9bf7</t>
+          <t>4a2c885b2b97079f0ee3eb71ba0294a8e0bd1e0241846e29018bfef6c669d8a0</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1255,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9858a46188f55c779e90cb2ad9c5175815e095a108a8cbbcdc49df4a8150d082</t>
+          <t>4e58756a9adde3cde9123001a795796197d85503330e55c5982f581a19ce2c9c</t>
         </is>
       </c>
     </row>
@@ -1221,11 +1266,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8213008</v>
+        <v>8195230</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>71d88f8281e172f2aa830cec8cacc07913854fafc2a359177d54ba8ebd08c0fc</t>
+          <t>7ba63eeca8abfff67fe81490a765b52756aa39d7f2dc555f415e9a4ab844a458</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1285,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>f1a673f152d003ec0ccd2604d1f45659d257613a70ed23ba084f500aef2a0153</t>
+          <t>ee6d9818d189843bd3caf917f47000b0cfd4efdef6cc7429a6679855d8f94e44</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1315,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>6232ad68b79e24d3b992c0079510ec1b59a5d9ee679f6599ca3874f8e13fe8a7</t>
+          <t>82ca09566044a067dcefe09e74f31bb591166521f5c6a565e55dd706c237135c</t>
         </is>
       </c>
     </row>
@@ -1296,11 +1341,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>48465</v>
+        <v>48538</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>730b2f94d9fcbe9bfde4aca7ce8829c7eff06c4315be4b41b0720eb39fed93c9</t>
+          <t>eadd3094a2ba9001b46403a28e4bc0842336441d52379e2d776275f7576c85d8</t>
         </is>
       </c>
     </row>
@@ -1311,11 +1356,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>522164</v>
+        <v>539959</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5f50c2068116e106b0c5dd96e3209370150d6c39b97c37cd5745865af55259c7</t>
+          <t>3783592511e27dd37446d891c95d88e70ad444942531f54820f8dbfa438f0a12</t>
         </is>
       </c>
     </row>
@@ -1326,11 +1371,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46055</v>
+        <v>46632</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>e556908408a3ba34f50eb2ede883d433c8069630f9d8af99f900b2b1c2fc2a1d</t>
+          <t>cee6adf8768452ab3e6bc51d366282f5e3e47e0a27e3d529ad9694fa558c1c23</t>
         </is>
       </c>
     </row>
@@ -1341,11 +1386,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1403616</v>
+        <v>1418876</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>d7b7305cef30def5a05aeb71a8d7755bcc605b2dadf1b1cee0213083897fa67d</t>
+          <t>d42e75853c77121516bbc34a59c005fdee056bff211907a1269b4708db19a0ec</t>
         </is>
       </c>
     </row>
@@ -1356,11 +1401,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>54113</v>
+        <v>62630</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>644283227d53b0b2fc098bf7bd9116a0b95813a15b4ff18e80b21d0a1afbec7b</t>
+          <t>36d1435b895663c57437fd29aaab9086893197a56f69315c5d2b621c0af2f53a</t>
         </is>
       </c>
     </row>
@@ -1371,11 +1416,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>562862</v>
+        <v>485743</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>9ee8f7f9ea67c07533b484d74b27c8805a6f4b40ba1477a5e55413c7b7a15c81</t>
+          <t>4a4df8d2534a8e0243234c7fefea0f790087286c99c6d133440375cf2746538f</t>
         </is>
       </c>
     </row>
@@ -1386,11 +1431,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>47952</v>
+        <v>56460</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>e507558aff8b096788647245815abeb98ada1d5aa8e51c5e4a4e6f557d3f4131</t>
+          <t>44561b3dd6615a31f363471691ca677dfaebc894715c2e886718b139046d87dc</t>
         </is>
       </c>
     </row>
@@ -1401,11 +1446,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1579692</v>
+        <v>1184486</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>541124b3e2845759ee6efc614136d2ea2910c745902074a08f84acfd63bf5830</t>
+          <t>6f1515b4f292b31cd8e07aa745dda6c40ee6d909210720763a96aa47dc7ec46f</t>
         </is>
       </c>
     </row>
@@ -1416,11 +1461,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9978</v>
+        <v>9982</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ef9112300c125d67d120e4d933e94ba8e6a2aca61707decab42401eee073de51</t>
+          <t>223293247fb2090398790d449c0c00d60598ddb3f63186a7682506944b8f8819</t>
         </is>
       </c>
     </row>
@@ -1431,11 +1476,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>527</v>
+        <v>588</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>c5b602e38089ced93aef7d6f360615bfa91d00232a1405e9700c61b3f023742e</t>
+          <t>5048899969dfd4afc8ef0ef3366cb3b49a36ac3dbbf2e20a97a5bc64d7d0b5c8</t>
         </is>
       </c>
     </row>
@@ -1446,11 +1491,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6089</v>
+        <v>6135</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>9eeba764dc13fbafdb6edef27a473caa7b44ee553ad77d86807e177eebccac48</t>
+          <t>622dfa827198041a5c77a2b7db593cd1e09712c059ce220b3da2566ca600c4d0</t>
         </is>
       </c>
     </row>
@@ -1461,11 +1506,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>71521</v>
+        <v>72590</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>b0d88272202dd86e51761f22e27ffcffb0849771a1f471f71085417eb12be126</t>
+          <t>a242fe8308920f756cfba9f2a758f4a9ec67fefba598c0c6da8818b0f9975995</t>
         </is>
       </c>
     </row>
@@ -1476,806 +1521,956 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>44211</v>
+        <v>44213</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ae200739a79ffb0595cccc5c789be243682a40c11e4a985e2dd26eeb877855d1</t>
+          <t>867f0a8a8ff663c7c289f4d8cf949efa6488e0924f92f9612d5d37fba449f0d1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>outputs/local/D7_d6_interface.schema.json</t>
+          <t>outputs/local/D7_edge_profile_summary.xlsx</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>705</v>
+        <v>26855</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>8622e18d50daee4e6d2038212b1778eeba5bfef0de9ac6300bfcf941e432f806</t>
+          <t>28ac73715e91e073705d114b17b361c0e5cf6e85d7511e8f8ec6184d24560156</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>outputs/local/D7_edge_profile_summary.xlsx</t>
+          <t>outputs/local/D7_event_windows.parquet</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>26855</v>
+        <v>80614</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>b1d07315b51a59aa649664e4664894b8f14175562e4b2bbb5ae81369bcb7afbf</t>
+          <t>b2163ad42fa4db796dbefc0b22ed5e24a96899ce26b09b41127e9acc35aa2050</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>outputs/local/D7_event_windows.parquet</t>
+          <t>outputs/local/D7_event_windows.xlsx</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>80611</v>
+        <v>140055</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>9fcea561c2e0bbe4bfae04fcaa8dbee3ee5cac2a49b024f49da946d8be3bb438</t>
+          <t>5483813be0904929e940be94d8f7ad17478d705ca8f9fd7be355ab9c1c530abc</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>outputs/local/D7_event_windows.xlsx</t>
+          <t>outputs/local/D7_gate_interface.parquet</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>139816</v>
+        <v>796803</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>d4f1d19b98c2264b1ec55ef284300e8969e67f88e2dc68d49fd6381ac0fe655c</t>
+          <t>fa843adf033668a81a6578f9540d3097d5b84d3a6ff8938ff444d871f171f094</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>outputs/local/D7_main_scores_hourly.parquet</t>
+          <t>outputs/local/D7_gate_interface.schema.json</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7276588</v>
+        <v>1106</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>7ed864bb1c9544b1da47c8624571e85323942f79a91e1e0f8a967891262638fb</t>
+          <t>07e9cd21efd998c1f25f3cc09aff2201b5541e096819a32387d08be4b381ba8d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>outputs/local/D7_main_scores_hourly.xlsx</t>
+          <t>outputs/local/D7_gate_interface.xlsx</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>38235544</v>
+        <v>5207136</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>8779022855420bab6ddd522ea9136455e9401ae3137feb9f08fc0999d651fd31</t>
+          <t>35a0f19497519eca83846bd8e453154f263ac270f362f4af26ea3e6d7897623e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>outputs/local/D7_mapping_params.xlsx</t>
+          <t>outputs/local/D7_main_scores_hourly.parquet</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>20246</v>
+        <v>7340577</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>4fe81c4a04825f07a7ec753b70a899cfc554d634f6900676cd81972f8d18c985</t>
+          <t>4774bac7c824f2b723a471d870fff58b018e05908f078de0b3ce6c3ae4c34d5f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>outputs/local/D7_multiscale_aggregates.xlsx</t>
+          <t>outputs/local/D7_main_scores_hourly.xlsx</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1060062</v>
+        <v>45264034</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>fb78a9faaa5f034e9c950f4012548d5e8152faadd4f7db37efa7b66995a6f584</t>
+          <t>3c879d87dce4adc96e88de88e73eb63cb050e8328e10de8c70894f0bc843c162</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>outputs/local/D7_reference_window_library.parquet</t>
+          <t>outputs/local/D7_mapping_params.xlsx</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>62947</v>
+        <v>20250</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>aae5eb4b04c93b812fbca7448a6b683799eb1b84f39df85b488f733b6d3617ee</t>
+          <t>6f60917072804e06f36a37086010c032b58290df9ecef5439419fc4c6cea4d70</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>outputs/local/D7_reference_window_library.xlsx</t>
+          <t>outputs/local/D7_multiscale_aggregates.xlsx</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>228948</v>
+        <v>1060059</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>a02fb9370975497897cb914af7caac1d9971f394e8efe1fbc2a0ea77bd1cdb98</t>
+          <t>dc7db20b2fd161ee51397bf844956527283c12e112f3213678c8b00367612a2c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>outputs/local/D7_regime_state.parquet</t>
+          <t>outputs/local/D7_reference_window_library.parquet</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3658910</v>
+        <v>62947</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>8a9662ff8a83352e56b209473677ed53089c4b8fb70e46cdbe8ada7cce0b9282</t>
+          <t>aae5eb4b04c93b812fbca7448a6b683799eb1b84f39df85b488f733b6d3617ee</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>outputs/local/D7_regime_state.xlsx</t>
+          <t>outputs/local/D7_reference_window_library.xlsx</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>45831285</v>
+        <v>228951</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>07c25e19aac80f2532bd845a6bd2d110e0d4feebac26cae3c2ed8077c9d65060</t>
+          <t>e8fa417c81bfc5adac89eb014beb68db72f019bc0d86f82b12b3a4bc020b5bab</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>outputs/local/D7_sensor_influence.parquet</t>
+          <t>outputs/local/D7_regime_state.parquet</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>5997938</v>
+        <v>3658910</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>effde4b688f5a8311f339749dedc6ab5ade2e072d636d5b5c806f153eafef7b1</t>
+          <t>cd0463070cd8bead73aebb99d205f5d89e5303f6d9f330b20858e7a38eb8f49b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>outputs/local/D7_sensor_influence.xlsx</t>
+          <t>outputs/local/D7_regime_state.xlsx</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>16393755</v>
+        <v>45838574</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>cddc1e8d23b587da537fe215e5368acad96c9b8aeec5ccef39e086bb153552f1</t>
+          <t>3a08b2ddd6959c023c76fa2ed4c2e637bb57428c6529ab3a74647868b657ba97</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>outputs/local/D7_sensor_profile_summary.xlsx</t>
+          <t>outputs/local/D7_report_interface.parquet</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7448</v>
+        <v>1171274</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>a0f2be8299a6e5e0f4470e0cc5692cbf97efd3f7c3d4c6c432330084a5d05ce0</t>
+          <t>b011811bc1d03a9312351a1ce3e1894660dffd3b604d35c4d5ef8c6430dc38f4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>outputs/local/D7_spatial_evidence.parquet</t>
+          <t>outputs/local/D7_report_interface.schema.json</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>6146149</v>
+        <v>834</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>328cbbfaf2e66d0ab412f0478724bb46c87861810d6907b0dba0a51470e76f9a</t>
+          <t>2b1373bb76f781f4adf2da91314f208b4d35d55b3479abbd44e68de67df0852e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>outputs/local/D7_spatial_evidence.xlsx</t>
+          <t>outputs/local/D7_report_interface.xlsx</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>15954460</v>
+        <v>11409135</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>7cce68ffcc78b5ce62403100980c55934017ff49be49127df7737d90a5167310</t>
+          <t>27029461cde48f7cf717ccf667fae604c4629820c0f1cfa8943acea5113c2fb8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>outputs/local/D7_spatial_templates.template_bundle.json</t>
+          <t>outputs/local/D7_sensor_influence.parquet</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>484477</v>
+        <v>6011235</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>d6b580520dfc3693969bddcbdcd74a992f3b215a68deb3e72ccab03a904c594e</t>
+          <t>0da1376646bba2c9cb1edef3a828d715a14bdd0ff76c6a283e0559e8bad1df5e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>outputs/local/D7_spatial_templates.xlsx</t>
+          <t>outputs/local/D7_sensor_influence.xlsx</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>184662</v>
+        <v>16404389</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3e5bedecbbdef9a50270118e4ebca98882236c60636de1fbc397c8b1d4801156</t>
+          <t>ba77bb8880db749c5b17149fb83d770ac918b79621bc4c2d902dd810da0bb85b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>outputs/local/D7_support_assessment.parquet</t>
+          <t>outputs/local/D7_sensor_profile_summary.xlsx</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>37484</v>
+        <v>7443</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>dbb000eae780a52bcbca5d0acf1436e1aa8457bcd7903e36f35dee2f32f5978a</t>
+          <t>05fb2e261a1184651ed2acd2b526f43ff803c36a44f36546ad9ad5cb22033b1d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>outputs/local/D7_support_assessment.xlsx</t>
+          <t>outputs/local/D7_spatial_evidence.parquet</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>21603</v>
+        <v>6146048</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>fe9166722fc5645ae185c9c0627c4a0f09463bce750a9b2f5ed92d5eff9065f9</t>
+          <t>3582f034468f5f610e15d1d704ef1415a304325380b5adc1c24a0002a670ed52</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>outputs/local/D7_topology_drift_alerts.parquet</t>
+          <t>outputs/local/D7_spatial_evidence.xlsx</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10824</v>
+        <v>15963330</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>3404956c892693273b3ded96268624a27bac9d0b3a29e0c0f00074ba1d7fed34</t>
+          <t>8e2489f0f8cb4b1314061a7e694305185d86afe29ae872d29250ebcbf882d3b7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>outputs/local/D7_topology_drift_alerts.xlsx</t>
+          <t>outputs/local/D7_spatial_templates.template_bundle.json</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>9963</v>
+        <v>542571</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>193e7854c5760d3ce9ed0924a83747bdb591abdd3b35ddc88bb5001790f49480</t>
+          <t>c694a28a951a6a9e5399206d7e6dc6e720a4a59f34e7ae9563ec58ef9cc97887</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>outputs/local/D7_topology_evidence.yaml</t>
+          <t>outputs/local/D7_spatial_templates.xlsx</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1780</v>
+        <v>190687</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>7c5cf9bbd05684af417f836b9e52474fb3d9d9fd6670131400f7587c50ff1d9f</t>
+          <t>15c9576ba437f28a9af8b9066b95abfbe73ef25b400af756e580b81778dd1567</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>outputs/local/D7_topology_registry.json</t>
+          <t>outputs/local/D7_support_assessment.parquet</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>14108</v>
+        <v>52816</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>e9cd1bd8356d3e22858f0a41236c01ac164109cccc5acd1529a536ffed1feb13</t>
+          <t>de562417a894df8430222fada206be2f2ac6ec5a78538d53cf5b5981afcc23fa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>outputs/local/D7_topology_registry.schema.json</t>
+          <t>outputs/local/D7_support_assessment.xlsx</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1263</v>
+        <v>28024</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3b6af16c6f624602a9851d780a2eb0d87f381ca851177c422c742d7fb60aed41</t>
+          <t>d52e94d44d8ef562375c37c7793502dedb8c78a015cff2b5ea8507a8bef5ae5c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>outputs/local/D7_topology_registry.xlsx</t>
+          <t>outputs/local/D7_topology_drift_alerts.parquet</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>11668</v>
+        <v>10824</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>b308ba74a034a2b8c6f0f2729d1c6c4efbae144ad3967090c361b85ec86b2f17</t>
+          <t>3404956c892693273b3ded96268624a27bac9d0b3a29e0c0f00074ba1d7fed34</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>outputs/local/D7_topology_registry.yaml</t>
+          <t>outputs/local/D7_topology_drift_alerts.xlsx</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2817</v>
+        <v>9963</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>31ff85866ebb7bc744c00a120199bb0f463b1e06459c0822fd76d14bea3ac396</t>
+          <t>e7f1aae79a137703de1962064dc8034b7ce16ed8d443ad5ad7b4d32c36128a62</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>outputs/local/D7_validation_results.xlsx</t>
+          <t>outputs/local/D7_topology_evidence.yaml</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>57844</v>
+        <v>1780</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>617213bbad3b8c6be6ba042b78b2e87baa06ccfa441eb2e03db61b695016ab8c</t>
+          <t>7c5cf9bbd05684af417f836b9e52474fb3d9d9fd6670131400f7587c50ff1d9f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>outputs/local/D7_zone_consensus.parquet</t>
+          <t>outputs/local/D7_topology_registry.json</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1619134</v>
+        <v>14108</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>a190943236ee77e3ef76eaf21161d36f85536a8f609a1f17fcefa7b94fa26fab</t>
+          <t>e9cd1bd8356d3e22858f0a41236c01ac164109cccc5acd1529a536ffed1feb13</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>outputs/local/D7_zone_consensus.xlsx</t>
+          <t>outputs/local/D7_topology_registry.schema.json</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>7173314</v>
+        <v>1263</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>cf108271ea387eee4cd7b9933f4a1d22666d473bbcd628c70b7b863b301febd4</t>
+          <t>3b6af16c6f624602a9851d780a2eb0d87f381ca851177c422c742d7fb60aed41</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>outputs/plot_data/D7_plot_data.csv</t>
+          <t>outputs/local/D7_topology_registry.xlsx</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>5441687</v>
+        <v>11671</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>f3d5e49114c0207025d1660687e19a8160e021b6a7cc04dfa3e682cd79a522e2</t>
+          <t>9178e91e4c46ffedfe5646efcc016fdac518cf78b8e33fbd99f4ba2dfc5ac4fb</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>outputs/plot_data/D7_plot_data.parquet</t>
+          <t>outputs/local/D7_topology_registry.yaml</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>181028</v>
+        <v>2817</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>72e325bcdcbb8bc42798f980d8141b32f093fd4d16606705cb141c551e60018b</t>
+          <t>31ff85866ebb7bc744c00a120199bb0f463b1e06459c0822fd76d14bea3ac396</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>outputs/plot_data/D7_plot_data_manifest.json</t>
+          <t>outputs/local/D7_validation_results.xlsx</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>519</v>
+        <v>60796</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>db706890dd73bfb07aba239ac3947b45b00cfd07c9fe38b4ae4b6012bbcf3687</t>
+          <t>bc412d7d06f4b7662c3f385aee8db9dd5d9070a8a3b82acb87a51d5563b575f4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>outputs/reports/D7_CURRENT_RELEASE.md</t>
+          <t>outputs/local/D7_zone_consensus.parquet</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>798</v>
+        <v>1618880</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>3d6fd45de0be626ac8e6573d82cdd1b56a2e54e342dc3a6a732e40f90a221439</t>
+          <t>f4331d395f3cfffbd653068b4da01d098a67580bf8c7687ae0f352cf9ad130bd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>outputs/reports/D7_EXPERT_REPORT_v2.1.docx</t>
+          <t>outputs/local/D7_zone_consensus.xlsx</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2047657</v>
+        <v>7274157</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>8e5db363b70bd05b8584eb191b764d1d2beee31c2be738b56f44c9902c67fb04</t>
+          <t>e8bf1928ab4ae30279e9e631521de9c490cd8924ea283fdd00cddb8f4c3c66fa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>outputs/reports/D7_EXPERT_REPORT_v2.1.md</t>
+          <t>outputs/plot_data/D7_plot_data.csv</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>7814</v>
+        <v>18506701</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2bbcb955dcc4c6e38b8cecc4735cc37412c05e80726817cb96aa200ca5fc9de7</t>
+          <t>08797f3cbd24d90ba19fce926a15ffef754aae65245cfef1342a5ad70b3d348d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>outputs/reports/D7_EXPERT_REPORT_v2.2.docx</t>
+          <t>outputs/plot_data/D7_plot_data.parquet</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2107226</v>
+        <v>744459</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>9dfbe96a145765a0e22e8452ec1a76f759ae52cd201b71694aa7c7e815fd8d8b</t>
+          <t>bc2b5c75fa95c12c2d71f368e5a13d0b47e667d88940b22100cfc2bc0570d7a1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>outputs/reports/D7_EXPERT_REPORT_v2.2.md</t>
+          <t>outputs/plot_data/D7_plot_data_manifest.json</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>8480</v>
+        <v>519</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>a4733fbd8adb037825f1596c3fb693fefc1f503de87cf75394285bed45b9643a</t>
+          <t>ad4824bf6af90c58640888be2208046b9fa1ac0066ccfbfd21ec25037cb9e039</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>outputs/reports/D7_FIGURE_CAPTIONS_v2.1.md</t>
+          <t>outputs/reports/D7_CURRENT_RELEASE.md</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2282</v>
+        <v>837</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>547f491e710fb84f3a797de918f83ec6c147542322e75f117c3e9b0c99f838b3</t>
+          <t>40fb38ae552a8ebf0bf6333bd26fc0977cb0ad8ecf69b02f233b74231c3513b7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>outputs/reports/D7_FIGURE_CAPTIONS_v2.2.md</t>
+          <t>outputs/reports/D7_EXPERT_REPORT_v2.1.docx</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2185</v>
+        <v>2047657</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2b24e422882af4cef3effc1b6a8a254ca4360ee3aadf5c9b50c8b9647240f34e</t>
+          <t>8e5db363b70bd05b8584eb191b764d1d2beee31c2be738b56f44c9902c67fb04</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>outputs/reports/D7_PROJECT_DIRECTORY_GUIDE_v2.1.docx</t>
+          <t>outputs/reports/D7_EXPERT_REPORT_v2.1.md</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>40336</v>
+        <v>7814</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>c2da3e9cca5ef0a5e83b63089e8deeb7299a7e0e7735c0b4751cd47f2fc47844</t>
+          <t>2bbcb955dcc4c6e38b8cecc4735cc37412c05e80726817cb96aa200ca5fc9de7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>outputs/reports/D7_PROJECT_DIRECTORY_GUIDE_v2.1.md</t>
+          <t>outputs/reports/D7_EXPERT_REPORT_v2.2.docx</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>5333</v>
+        <v>2107226</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>53cf387245c96ec939711213a77e6bb90e05a4dbc46efdad326733199d129dfc</t>
+          <t>9dfbe96a145765a0e22e8452ec1a76f759ae52cd201b71694aa7c7e815fd8d8b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>outputs/reports/D7_PROJECT_DIRECTORY_GUIDE_v2.2.docx</t>
+          <t>outputs/reports/D7_EXPERT_REPORT_v2.2.md</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>40363</v>
+        <v>8480</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>eada32c51f435a6355dc873b748b4f894cbbc17bedfc4be6090371aa323aea5e</t>
+          <t>a4733fbd8adb037825f1596c3fb693fefc1f503de87cf75394285bed45b9643a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>outputs/reports/D7_PROJECT_DIRECTORY_GUIDE_v2.2.md</t>
+          <t>outputs/reports/D7_EXPERT_REPORT_v2.3.docx</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>5307</v>
+        <v>2056642</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>7db2ba45b38b3a23cc0d008dca2dbe2836fb57579d074f87cc4a91408691b049</t>
+          <t>d9cd85672b7e1d750c5a5ead16e7d1ec8423d890a6b566862f267ab6268ca4ab</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>outputs/sensitivity/D7_sensitivity_manifest.json</t>
+          <t>outputs/reports/D7_EXPERT_REPORT_v2.3.md</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2295</v>
+        <v>9043</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>326a08902801986e2a51b1068385a9ab56a47a84ae396dfe31a348530c892189</t>
+          <t>ca41c3ed66e50d3e998faa1aa6ddb7e39bddaf7481bb4d89e5706edc7ea49512</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>outputs/sensitivity/D7_shadow_scores.parquet</t>
+          <t>outputs/reports/D7_FIGURE_CAPTIONS_v2.1.md</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2987557</v>
+        <v>2282</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>7b805bcc76ceaa6a70302aee08a356b3e88f53159e0e8d7b35c10ae795a02866</t>
+          <t>547f491e710fb84f3a797de918f83ec6c147542322e75f117c3e9b0c99f838b3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>outputs/sensitivity/D7_shadow_scores.xlsx</t>
+          <t>outputs/reports/D7_FIGURE_CAPTIONS_v2.2.md</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>9995971</v>
+        <v>2185</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>002c222f5715022d748e2af984b8df750e63f3c1648bcaa74a78323d8a9a4c36</t>
+          <t>2b24e422882af4cef3effc1b6a8a254ca4360ee3aadf5c9b50c8b9647240f34e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>outputs/sensitivity/D7_shadow_template_shift.xlsx</t>
+          <t>outputs/reports/D7_FIGURE_CAPTIONS_v2.3.md</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>41681</v>
+        <v>2471</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>80abe875960c9007b872c61beaef5c614b3f7e3e862eac42b1ffc9fdf2d086d3</t>
+          <t>0d34e02ca322ccf7c19dfddc7c4978264fca40ef765a74346a571a21f44abafb</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>outputs/sensitivity/D7_track_invariance.xlsx</t>
+          <t>outputs/reports/D7_PROJECT_DIRECTORY_GUIDE_v2.1.docx</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>14539</v>
+        <v>40336</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>fe23a84e0175d36bf92f94c233f615dabc10ede522ae4609bf1bce29c19185c0</t>
+          <t>c2da3e9cca5ef0a5e83b63089e8deeb7299a7e0e7735c0b4751cd47f2fc47844</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>outputs/shadow_v2/D7_graph_structure_learning_shadow.parquet</t>
+          <t>outputs/reports/D7_PROJECT_DIRECTORY_GUIDE_v2.1.md</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>9388</v>
+        <v>5333</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>4bd0f7358453a59844087925fc0f654f50c3bca0517ee4bee8700cc672f0fd8c</t>
+          <t>53cf387245c96ec939711213a77e6bb90e05a4dbc46efdad326733199d129dfc</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>outputs/shadow_v2/D7_graph_structure_learning_shadow.xlsx</t>
+          <t>outputs/reports/D7_PROJECT_DIRECTORY_GUIDE_v2.2.docx</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>8325</v>
+        <v>40363</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>8c53710b85aae9d64fb2951424da37ae2d062f592364bb8da2105977040cc95e</t>
+          <t>eada32c51f435a6355dc873b748b4f894cbbc17bedfc4be6090371aa323aea5e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>outputs/reports/D7_PROJECT_DIRECTORY_GUIDE_v2.2.md</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>5307</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>7db2ba45b38b3a23cc0d008dca2dbe2836fb57579d074f87cc4a91408691b049</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>outputs/reports/D7_PROJECT_DIRECTORY_GUIDE_v2.3.docx</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>40363</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ffbb5b0590d1b15574f9537140dda2e194dcf2c2e8a6d704a70fb52fcedff430</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>outputs/reports/D7_PROJECT_DIRECTORY_GUIDE_v2.3.md</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>5459</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>b840daa5fd0296b3056363514351eddb19ab365671cdf4569d8fef25fd1d588e</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>outputs/sensitivity/D7_sensitivity_manifest.json</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>2345</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>15504c565c59993c6b77f9bed842902051f004260dc1fc78759a677fad220f24</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>outputs/sensitivity/D7_shadow_scores.parquet</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>2987622</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>bfc0ddd69f4710aec6153e746461a184d52245afdd2b2556e9237dcbad5d7899</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>outputs/sensitivity/D7_shadow_scores.xlsx</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>10000424</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>8867d880e6e46ffadc548cc9095bcf44dca0d39aebba64d95f8d0659b95f2ddd</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>outputs/sensitivity/D7_shadow_template_shift.xlsx</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>41680</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>e32226586518d777384ecb5eb205a755ee04a8edeca1d60d8b17a50edc77075f</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>outputs/sensitivity/D7_track_invariance.xlsx</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>14538</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>24f1ce493e50c9b58fde1cd487b4e33a191de2a6ca2761682acb67ecf8ef4cfb</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>outputs/shadow_v2/D7_graph_structure_learning_shadow.parquet</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>9388</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>4bd0f7358453a59844087925fc0f654f50c3bca0517ee4bee8700cc672f0fd8c</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>outputs/shadow_v2/D7_graph_structure_learning_shadow.xlsx</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>8325</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>8290f9a1766be1587ebe7f9f8deceb128e5b3968674674ae5af36dc445e5ff87</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>outputs/shadow_v2/D7_shadow_v2_manifest.json</t>
         </is>
       </c>
-      <c r="B81" t="n">
+      <c r="B91" t="n">
         <v>263</v>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>437108b43eec9a2261ac2bfa6ec7bfd3903191bfb24d85222ba28b0a425d3cc2</t>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2de3ff9108cd0acbf9490db68bd0b93a3ce1e4cde602cd376994e6ef2e580c5e</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3825,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2643264993521892</v>
+        <v>0.2643264993521895</v>
       </c>
       <c r="G30" t="n">
         <v>30</v>
@@ -3665,7 +3860,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2643264993521892</v>
+        <v>0.2643264993521895</v>
       </c>
       <c r="G31" t="n">
         <v>30</v>
@@ -3700,7 +3895,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2643264993521892</v>
+        <v>0.2643264993521895</v>
       </c>
       <c r="G32" t="n">
         <v>30</v>
@@ -3735,7 +3930,7 @@
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2643264993521892</v>
+        <v>0.2643264993521895</v>
       </c>
       <c r="G33" t="n">
         <v>30</v>
@@ -3770,7 +3965,7 @@
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2643264993521892</v>
+        <v>0.2643264993521895</v>
       </c>
       <c r="G34" t="n">
         <v>30</v>
@@ -3805,7 +4000,7 @@
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2643264993521892</v>
+        <v>0.2643264993521895</v>
       </c>
       <c r="G35" t="n">
         <v>30</v>
@@ -3840,7 +4035,7 @@
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2643264993521892</v>
+        <v>0.2643264993521895</v>
       </c>
       <c r="G36" t="n">
         <v>30</v>
@@ -3875,7 +4070,7 @@
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2643264993521892</v>
+        <v>0.2643264993521895</v>
       </c>
       <c r="G37" t="n">
         <v>30</v>
@@ -3910,7 +4105,7 @@
         <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2643264993521892</v>
+        <v>0.2643264993521895</v>
       </c>
       <c r="G38" t="n">
         <v>30</v>
@@ -3945,7 +4140,7 @@
         <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2643264993521892</v>
+        <v>0.2643264993521895</v>
       </c>
       <c r="G39" t="n">
         <v>30</v>
@@ -3980,7 +4175,7 @@
         <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2643264993521892</v>
+        <v>0.2643264993521895</v>
       </c>
       <c r="G40" t="n">
         <v>30</v>
@@ -4015,7 +4210,7 @@
         <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2643264993521892</v>
+        <v>0.2643264993521895</v>
       </c>
       <c r="G41" t="n">
         <v>30</v>
@@ -4050,7 +4245,7 @@
         <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2643264993521892</v>
+        <v>0.2643264993521895</v>
       </c>
       <c r="G42" t="n">
         <v>30</v>
@@ -4085,7 +4280,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2643264993521892</v>
+        <v>0.2643264993521895</v>
       </c>
       <c r="G43" t="n">
         <v>30</v>
@@ -4610,7 +4805,7 @@
         <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>0.4847581538360898</v>
+        <v>0.4847581538360896</v>
       </c>
       <c r="G58" t="n">
         <v>30</v>
@@ -4645,7 +4840,7 @@
         <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4847581538360898</v>
+        <v>0.4847581538360896</v>
       </c>
       <c r="G59" t="n">
         <v>30</v>
@@ -4680,7 +4875,7 @@
         <v>1</v>
       </c>
       <c r="F60" t="n">
-        <v>0.4847581538360898</v>
+        <v>0.4847581538360896</v>
       </c>
       <c r="G60" t="n">
         <v>30</v>
@@ -4715,7 +4910,7 @@
         <v>1</v>
       </c>
       <c r="F61" t="n">
-        <v>0.4847581538360898</v>
+        <v>0.4847581538360896</v>
       </c>
       <c r="G61" t="n">
         <v>30</v>
@@ -4750,7 +4945,7 @@
         <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>0.4847581538360898</v>
+        <v>0.4847581538360896</v>
       </c>
       <c r="G62" t="n">
         <v>30</v>
@@ -4785,7 +4980,7 @@
         <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>0.4847581538360898</v>
+        <v>0.4847581538360896</v>
       </c>
       <c r="G63" t="n">
         <v>30</v>
@@ -4820,7 +5015,7 @@
         <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>0.4847581538360898</v>
+        <v>0.4847581538360896</v>
       </c>
       <c r="G64" t="n">
         <v>30</v>
@@ -4855,7 +5050,7 @@
         <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>0.4847581538360898</v>
+        <v>0.4847581538360896</v>
       </c>
       <c r="G65" t="n">
         <v>30</v>
@@ -4890,7 +5085,7 @@
         <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>0.4847581538360898</v>
+        <v>0.4847581538360896</v>
       </c>
       <c r="G66" t="n">
         <v>30</v>
@@ -4925,7 +5120,7 @@
         <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>0.4847581538360898</v>
+        <v>0.4847581538360896</v>
       </c>
       <c r="G67" t="n">
         <v>30</v>
@@ -4960,7 +5155,7 @@
         <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>0.4847581538360898</v>
+        <v>0.4847581538360896</v>
       </c>
       <c r="G68" t="n">
         <v>30</v>
@@ -4995,7 +5190,7 @@
         <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>0.4847581538360898</v>
+        <v>0.4847581538360896</v>
       </c>
       <c r="G69" t="n">
         <v>30</v>
@@ -5030,7 +5225,7 @@
         <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>0.4847581538360898</v>
+        <v>0.4847581538360896</v>
       </c>
       <c r="G70" t="n">
         <v>30</v>
@@ -5065,7 +5260,7 @@
         <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>0.4847581538360898</v>
+        <v>0.4847581538360896</v>
       </c>
       <c r="G71" t="n">
         <v>30</v>
@@ -6080,7 +6275,7 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G100" t="n">
         <v>30</v>
@@ -6115,7 +6310,7 @@
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G101" t="n">
         <v>30</v>
@@ -6150,7 +6345,7 @@
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G102" t="n">
         <v>30</v>
@@ -6185,7 +6380,7 @@
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G103" t="n">
         <v>30</v>
@@ -6220,7 +6415,7 @@
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G104" t="n">
         <v>30</v>
@@ -6255,7 +6450,7 @@
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G105" t="n">
         <v>30</v>
@@ -6290,7 +6485,7 @@
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G106" t="n">
         <v>30</v>
@@ -6325,7 +6520,7 @@
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G107" t="n">
         <v>30</v>
@@ -6360,7 +6555,7 @@
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G108" t="n">
         <v>30</v>
@@ -6395,7 +6590,7 @@
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G109" t="n">
         <v>30</v>
@@ -6430,7 +6625,7 @@
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G110" t="n">
         <v>30</v>
@@ -6465,7 +6660,7 @@
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G111" t="n">
         <v>30</v>
@@ -6500,7 +6695,7 @@
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G112" t="n">
         <v>30</v>
@@ -6535,7 +6730,7 @@
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G113" t="n">
         <v>30</v>
@@ -6570,7 +6765,7 @@
         <v>1</v>
       </c>
       <c r="F114" t="n">
-        <v>0.2509769079423547</v>
+        <v>0.2509769079423544</v>
       </c>
       <c r="G114" t="n">
         <v>30</v>
@@ -6605,7 +6800,7 @@
         <v>1</v>
       </c>
       <c r="F115" t="n">
-        <v>0.2509769079423547</v>
+        <v>0.2509769079423544</v>
       </c>
       <c r="G115" t="n">
         <v>30</v>
@@ -6640,7 +6835,7 @@
         <v>1</v>
       </c>
       <c r="F116" t="n">
-        <v>0.2509769079423547</v>
+        <v>0.2509769079423544</v>
       </c>
       <c r="G116" t="n">
         <v>30</v>
@@ -6675,7 +6870,7 @@
         <v>1</v>
       </c>
       <c r="F117" t="n">
-        <v>0.2509769079423547</v>
+        <v>0.2509769079423544</v>
       </c>
       <c r="G117" t="n">
         <v>30</v>
@@ -6710,7 +6905,7 @@
         <v>1</v>
       </c>
       <c r="F118" t="n">
-        <v>0.2509769079423547</v>
+        <v>0.2509769079423544</v>
       </c>
       <c r="G118" t="n">
         <v>30</v>
@@ -6745,7 +6940,7 @@
         <v>1</v>
       </c>
       <c r="F119" t="n">
-        <v>0.2509769079423547</v>
+        <v>0.2509769079423544</v>
       </c>
       <c r="G119" t="n">
         <v>30</v>
@@ -6780,7 +6975,7 @@
         <v>1</v>
       </c>
       <c r="F120" t="n">
-        <v>0.2509769079423547</v>
+        <v>0.2509769079423544</v>
       </c>
       <c r="G120" t="n">
         <v>30</v>
@@ -6815,7 +7010,7 @@
         <v>1</v>
       </c>
       <c r="F121" t="n">
-        <v>0.2509769079423547</v>
+        <v>0.2509769079423544</v>
       </c>
       <c r="G121" t="n">
         <v>30</v>
@@ -6850,7 +7045,7 @@
         <v>1</v>
       </c>
       <c r="F122" t="n">
-        <v>0.2509769079423547</v>
+        <v>0.2509769079423544</v>
       </c>
       <c r="G122" t="n">
         <v>30</v>
@@ -6885,7 +7080,7 @@
         <v>1</v>
       </c>
       <c r="F123" t="n">
-        <v>0.2509769079423547</v>
+        <v>0.2509769079423544</v>
       </c>
       <c r="G123" t="n">
         <v>30</v>
@@ -6920,7 +7115,7 @@
         <v>1</v>
       </c>
       <c r="F124" t="n">
-        <v>0.2509769079423547</v>
+        <v>0.2509769079423544</v>
       </c>
       <c r="G124" t="n">
         <v>30</v>
@@ -6955,7 +7150,7 @@
         <v>1</v>
       </c>
       <c r="F125" t="n">
-        <v>0.2509769079423547</v>
+        <v>0.2509769079423544</v>
       </c>
       <c r="G125" t="n">
         <v>30</v>
@@ -6990,7 +7185,7 @@
         <v>1</v>
       </c>
       <c r="F126" t="n">
-        <v>0.2509769079423547</v>
+        <v>0.2509769079423544</v>
       </c>
       <c r="G126" t="n">
         <v>30</v>
@@ -7025,7 +7220,7 @@
         <v>1</v>
       </c>
       <c r="F127" t="n">
-        <v>0.2509769079423547</v>
+        <v>0.2509769079423544</v>
       </c>
       <c r="G127" t="n">
         <v>30</v>
@@ -9020,7 +9215,7 @@
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>0.6122137226253055</v>
+        <v>0.6122137226253057</v>
       </c>
       <c r="G184" t="n">
         <v>30</v>
@@ -9055,7 +9250,7 @@
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>0.6122137226253055</v>
+        <v>0.6122137226253057</v>
       </c>
       <c r="G185" t="n">
         <v>30</v>
@@ -9090,7 +9285,7 @@
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>0.6122137226253055</v>
+        <v>0.6122137226253057</v>
       </c>
       <c r="G186" t="n">
         <v>30</v>
@@ -9125,7 +9320,7 @@
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>0.6122137226253055</v>
+        <v>0.6122137226253057</v>
       </c>
       <c r="G187" t="n">
         <v>30</v>
@@ -9160,7 +9355,7 @@
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>0.6122137226253055</v>
+        <v>0.6122137226253057</v>
       </c>
       <c r="G188" t="n">
         <v>30</v>
@@ -9195,7 +9390,7 @@
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>0.6122137226253055</v>
+        <v>0.6122137226253057</v>
       </c>
       <c r="G189" t="n">
         <v>30</v>
@@ -9230,7 +9425,7 @@
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>0.6122137226253055</v>
+        <v>0.6122137226253057</v>
       </c>
       <c r="G190" t="n">
         <v>30</v>
@@ -9265,7 +9460,7 @@
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>0.6122137226253055</v>
+        <v>0.6122137226253057</v>
       </c>
       <c r="G191" t="n">
         <v>30</v>
@@ -9300,7 +9495,7 @@
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>0.6122137226253055</v>
+        <v>0.6122137226253057</v>
       </c>
       <c r="G192" t="n">
         <v>30</v>
@@ -9335,7 +9530,7 @@
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>0.6122137226253055</v>
+        <v>0.6122137226253057</v>
       </c>
       <c r="G193" t="n">
         <v>30</v>
@@ -9370,7 +9565,7 @@
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>0.6122137226253055</v>
+        <v>0.6122137226253057</v>
       </c>
       <c r="G194" t="n">
         <v>30</v>
@@ -9405,7 +9600,7 @@
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>0.6122137226253055</v>
+        <v>0.6122137226253057</v>
       </c>
       <c r="G195" t="n">
         <v>30</v>
@@ -9440,7 +9635,7 @@
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>0.6122137226253055</v>
+        <v>0.6122137226253057</v>
       </c>
       <c r="G196" t="n">
         <v>30</v>
@@ -9475,7 +9670,7 @@
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>0.6122137226253055</v>
+        <v>0.6122137226253057</v>
       </c>
       <c r="G197" t="n">
         <v>30</v>
@@ -10980,7 +11175,7 @@
         <v>0</v>
       </c>
       <c r="F240" t="n">
-        <v>0.56516291541854</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G240" t="n">
         <v>30</v>
@@ -11015,7 +11210,7 @@
         <v>0</v>
       </c>
       <c r="F241" t="n">
-        <v>0.56516291541854</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G241" t="n">
         <v>30</v>
@@ -11050,7 +11245,7 @@
         <v>0</v>
       </c>
       <c r="F242" t="n">
-        <v>0.56516291541854</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G242" t="n">
         <v>30</v>
@@ -11085,7 +11280,7 @@
         <v>0</v>
       </c>
       <c r="F243" t="n">
-        <v>0.56516291541854</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G243" t="n">
         <v>30</v>
@@ -11120,7 +11315,7 @@
         <v>0</v>
       </c>
       <c r="F244" t="n">
-        <v>0.56516291541854</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G244" t="n">
         <v>30</v>
@@ -11155,7 +11350,7 @@
         <v>0</v>
       </c>
       <c r="F245" t="n">
-        <v>0.56516291541854</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G245" t="n">
         <v>30</v>
@@ -11190,7 +11385,7 @@
         <v>0</v>
       </c>
       <c r="F246" t="n">
-        <v>0.56516291541854</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G246" t="n">
         <v>30</v>
@@ -11225,7 +11420,7 @@
         <v>0</v>
       </c>
       <c r="F247" t="n">
-        <v>0.56516291541854</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G247" t="n">
         <v>30</v>
@@ -11260,7 +11455,7 @@
         <v>0</v>
       </c>
       <c r="F248" t="n">
-        <v>0.56516291541854</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G248" t="n">
         <v>30</v>
@@ -11295,7 +11490,7 @@
         <v>0</v>
       </c>
       <c r="F249" t="n">
-        <v>0.56516291541854</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G249" t="n">
         <v>30</v>
@@ -11330,7 +11525,7 @@
         <v>0</v>
       </c>
       <c r="F250" t="n">
-        <v>0.56516291541854</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G250" t="n">
         <v>30</v>
@@ -11365,7 +11560,7 @@
         <v>0</v>
       </c>
       <c r="F251" t="n">
-        <v>0.56516291541854</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G251" t="n">
         <v>30</v>
@@ -11400,7 +11595,7 @@
         <v>0</v>
       </c>
       <c r="F252" t="n">
-        <v>0.56516291541854</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G252" t="n">
         <v>30</v>
@@ -11435,7 +11630,7 @@
         <v>0</v>
       </c>
       <c r="F253" t="n">
-        <v>0.56516291541854</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G253" t="n">
         <v>30</v>
@@ -11960,7 +12155,7 @@
         <v>0</v>
       </c>
       <c r="F268" t="n">
-        <v>0.4041894705462785</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G268" t="n">
         <v>30</v>
@@ -11995,7 +12190,7 @@
         <v>0</v>
       </c>
       <c r="F269" t="n">
-        <v>0.4041894705462785</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G269" t="n">
         <v>30</v>
@@ -12030,7 +12225,7 @@
         <v>0</v>
       </c>
       <c r="F270" t="n">
-        <v>0.4041894705462785</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G270" t="n">
         <v>30</v>
@@ -12065,7 +12260,7 @@
         <v>0</v>
       </c>
       <c r="F271" t="n">
-        <v>0.4041894705462785</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G271" t="n">
         <v>30</v>
@@ -12100,7 +12295,7 @@
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0.4041894705462785</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G272" t="n">
         <v>30</v>
@@ -12135,7 +12330,7 @@
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0.4041894705462785</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G273" t="n">
         <v>30</v>
@@ -12170,7 +12365,7 @@
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0.4041894705462785</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G274" t="n">
         <v>30</v>
@@ -12205,7 +12400,7 @@
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0.4041894705462785</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G275" t="n">
         <v>30</v>
@@ -12240,7 +12435,7 @@
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0.4041894705462785</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G276" t="n">
         <v>30</v>
@@ -12275,7 +12470,7 @@
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0.4041894705462785</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G277" t="n">
         <v>30</v>
@@ -12310,7 +12505,7 @@
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0.4041894705462785</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G278" t="n">
         <v>30</v>
@@ -12345,7 +12540,7 @@
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0.4041894705462785</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G279" t="n">
         <v>30</v>
@@ -12380,7 +12575,7 @@
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0.4041894705462785</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G280" t="n">
         <v>30</v>
@@ -12415,7 +12610,7 @@
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0.4041894705462785</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G281" t="n">
         <v>30</v>
@@ -12940,7 +13135,7 @@
         <v>0</v>
       </c>
       <c r="F296" t="n">
-        <v>0.7707808739610936</v>
+        <v>0.7707808739610937</v>
       </c>
       <c r="G296" t="n">
         <v>30</v>
@@ -12975,7 +13170,7 @@
         <v>0</v>
       </c>
       <c r="F297" t="n">
-        <v>0.7707808739610936</v>
+        <v>0.7707808739610937</v>
       </c>
       <c r="G297" t="n">
         <v>30</v>
@@ -13010,7 +13205,7 @@
         <v>0</v>
       </c>
       <c r="F298" t="n">
-        <v>0.7707808739610936</v>
+        <v>0.7707808739610937</v>
       </c>
       <c r="G298" t="n">
         <v>30</v>
@@ -13045,7 +13240,7 @@
         <v>0</v>
       </c>
       <c r="F299" t="n">
-        <v>0.7707808739610936</v>
+        <v>0.7707808739610937</v>
       </c>
       <c r="G299" t="n">
         <v>30</v>
@@ -13080,7 +13275,7 @@
         <v>0</v>
       </c>
       <c r="F300" t="n">
-        <v>0.7707808739610936</v>
+        <v>0.7707808739610937</v>
       </c>
       <c r="G300" t="n">
         <v>30</v>
@@ -13115,7 +13310,7 @@
         <v>0</v>
       </c>
       <c r="F301" t="n">
-        <v>0.7707808739610936</v>
+        <v>0.7707808739610937</v>
       </c>
       <c r="G301" t="n">
         <v>30</v>
@@ -13150,7 +13345,7 @@
         <v>0</v>
       </c>
       <c r="F302" t="n">
-        <v>0.7707808739610936</v>
+        <v>0.7707808739610937</v>
       </c>
       <c r="G302" t="n">
         <v>30</v>
@@ -13185,7 +13380,7 @@
         <v>0</v>
       </c>
       <c r="F303" t="n">
-        <v>0.7707808739610936</v>
+        <v>0.7707808739610937</v>
       </c>
       <c r="G303" t="n">
         <v>30</v>
@@ -13220,7 +13415,7 @@
         <v>0</v>
       </c>
       <c r="F304" t="n">
-        <v>0.7707808739610936</v>
+        <v>0.7707808739610937</v>
       </c>
       <c r="G304" t="n">
         <v>30</v>
@@ -13255,7 +13450,7 @@
         <v>0</v>
       </c>
       <c r="F305" t="n">
-        <v>0.7707808739610936</v>
+        <v>0.7707808739610937</v>
       </c>
       <c r="G305" t="n">
         <v>30</v>
@@ -13290,7 +13485,7 @@
         <v>0</v>
       </c>
       <c r="F306" t="n">
-        <v>0.7707808739610936</v>
+        <v>0.7707808739610937</v>
       </c>
       <c r="G306" t="n">
         <v>30</v>
@@ -13325,7 +13520,7 @@
         <v>0</v>
       </c>
       <c r="F307" t="n">
-        <v>0.7707808739610936</v>
+        <v>0.7707808739610937</v>
       </c>
       <c r="G307" t="n">
         <v>30</v>
@@ -13360,7 +13555,7 @@
         <v>0</v>
       </c>
       <c r="F308" t="n">
-        <v>0.7707808739610936</v>
+        <v>0.7707808739610937</v>
       </c>
       <c r="G308" t="n">
         <v>30</v>
@@ -13395,7 +13590,7 @@
         <v>0</v>
       </c>
       <c r="F309" t="n">
-        <v>0.7707808739610936</v>
+        <v>0.7707808739610937</v>
       </c>
       <c r="G309" t="n">
         <v>30</v>
@@ -17350,7 +17545,7 @@
         <v>1</v>
       </c>
       <c r="F422" t="n">
-        <v>0.3542208532264322</v>
+        <v>0.3542208532264326</v>
       </c>
       <c r="G422" t="n">
         <v>30</v>
@@ -17385,7 +17580,7 @@
         <v>1</v>
       </c>
       <c r="F423" t="n">
-        <v>0.3542208532264322</v>
+        <v>0.3542208532264326</v>
       </c>
       <c r="G423" t="n">
         <v>30</v>
@@ -17420,7 +17615,7 @@
         <v>1</v>
       </c>
       <c r="F424" t="n">
-        <v>0.3542208532264322</v>
+        <v>0.3542208532264326</v>
       </c>
       <c r="G424" t="n">
         <v>30</v>
@@ -17455,7 +17650,7 @@
         <v>1</v>
       </c>
       <c r="F425" t="n">
-        <v>0.3542208532264322</v>
+        <v>0.3542208532264326</v>
       </c>
       <c r="G425" t="n">
         <v>30</v>
@@ -17490,7 +17685,7 @@
         <v>1</v>
       </c>
       <c r="F426" t="n">
-        <v>0.3542208532264322</v>
+        <v>0.3542208532264326</v>
       </c>
       <c r="G426" t="n">
         <v>30</v>
@@ -17525,7 +17720,7 @@
         <v>1</v>
       </c>
       <c r="F427" t="n">
-        <v>0.3542208532264322</v>
+        <v>0.3542208532264326</v>
       </c>
       <c r="G427" t="n">
         <v>30</v>
@@ -17560,7 +17755,7 @@
         <v>1</v>
       </c>
       <c r="F428" t="n">
-        <v>0.3542208532264322</v>
+        <v>0.3542208532264326</v>
       </c>
       <c r="G428" t="n">
         <v>30</v>
@@ -17595,7 +17790,7 @@
         <v>1</v>
       </c>
       <c r="F429" t="n">
-        <v>0.3542208532264322</v>
+        <v>0.3542208532264326</v>
       </c>
       <c r="G429" t="n">
         <v>30</v>
@@ -17630,7 +17825,7 @@
         <v>1</v>
       </c>
       <c r="F430" t="n">
-        <v>0.3542208532264322</v>
+        <v>0.3542208532264326</v>
       </c>
       <c r="G430" t="n">
         <v>30</v>
@@ -17665,7 +17860,7 @@
         <v>1</v>
       </c>
       <c r="F431" t="n">
-        <v>0.3542208532264322</v>
+        <v>0.3542208532264326</v>
       </c>
       <c r="G431" t="n">
         <v>30</v>
@@ -17700,7 +17895,7 @@
         <v>1</v>
       </c>
       <c r="F432" t="n">
-        <v>0.3542208532264322</v>
+        <v>0.3542208532264326</v>
       </c>
       <c r="G432" t="n">
         <v>30</v>
@@ -17735,7 +17930,7 @@
         <v>1</v>
       </c>
       <c r="F433" t="n">
-        <v>0.3542208532264322</v>
+        <v>0.3542208532264326</v>
       </c>
       <c r="G433" t="n">
         <v>30</v>
@@ -17770,7 +17965,7 @@
         <v>1</v>
       </c>
       <c r="F434" t="n">
-        <v>0.3542208532264322</v>
+        <v>0.3542208532264326</v>
       </c>
       <c r="G434" t="n">
         <v>30</v>
@@ -17805,7 +18000,7 @@
         <v>1</v>
       </c>
       <c r="F435" t="n">
-        <v>0.3542208532264322</v>
+        <v>0.3542208532264326</v>
       </c>
       <c r="G435" t="n">
         <v>30</v>
@@ -17840,7 +18035,7 @@
         <v>0</v>
       </c>
       <c r="F436" t="n">
-        <v>0.3064468083320384</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G436" t="n">
         <v>30</v>
@@ -17875,7 +18070,7 @@
         <v>0</v>
       </c>
       <c r="F437" t="n">
-        <v>0.3064468083320384</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G437" t="n">
         <v>30</v>
@@ -17910,7 +18105,7 @@
         <v>0</v>
       </c>
       <c r="F438" t="n">
-        <v>0.3064468083320384</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G438" t="n">
         <v>30</v>
@@ -17945,7 +18140,7 @@
         <v>0</v>
       </c>
       <c r="F439" t="n">
-        <v>0.3064468083320384</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G439" t="n">
         <v>30</v>
@@ -17980,7 +18175,7 @@
         <v>0</v>
       </c>
       <c r="F440" t="n">
-        <v>0.3064468083320384</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G440" t="n">
         <v>30</v>
@@ -18015,7 +18210,7 @@
         <v>0</v>
       </c>
       <c r="F441" t="n">
-        <v>0.3064468083320384</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G441" t="n">
         <v>30</v>
@@ -18050,7 +18245,7 @@
         <v>0</v>
       </c>
       <c r="F442" t="n">
-        <v>0.3064468083320384</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G442" t="n">
         <v>30</v>
@@ -18085,7 +18280,7 @@
         <v>0</v>
       </c>
       <c r="F443" t="n">
-        <v>0.3064468083320384</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G443" t="n">
         <v>30</v>
@@ -18120,7 +18315,7 @@
         <v>0</v>
       </c>
       <c r="F444" t="n">
-        <v>0.3064468083320384</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G444" t="n">
         <v>30</v>
@@ -18155,7 +18350,7 @@
         <v>0</v>
       </c>
       <c r="F445" t="n">
-        <v>0.3064468083320384</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G445" t="n">
         <v>30</v>
@@ -18190,7 +18385,7 @@
         <v>0</v>
       </c>
       <c r="F446" t="n">
-        <v>0.3064468083320384</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G446" t="n">
         <v>30</v>
@@ -18225,7 +18420,7 @@
         <v>0</v>
       </c>
       <c r="F447" t="n">
-        <v>0.3064468083320384</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G447" t="n">
         <v>30</v>
@@ -18260,7 +18455,7 @@
         <v>0</v>
       </c>
       <c r="F448" t="n">
-        <v>0.3064468083320384</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G448" t="n">
         <v>30</v>
@@ -18295,7 +18490,7 @@
         <v>0</v>
       </c>
       <c r="F449" t="n">
-        <v>0.3064468083320384</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G449" t="n">
         <v>30</v>
@@ -18820,7 +19015,7 @@
         <v>0</v>
       </c>
       <c r="F464" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G464" t="n">
         <v>30</v>
@@ -18855,7 +19050,7 @@
         <v>0</v>
       </c>
       <c r="F465" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G465" t="n">
         <v>30</v>
@@ -18890,7 +19085,7 @@
         <v>0</v>
       </c>
       <c r="F466" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G466" t="n">
         <v>30</v>
@@ -18925,7 +19120,7 @@
         <v>0</v>
       </c>
       <c r="F467" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G467" t="n">
         <v>30</v>
@@ -18960,7 +19155,7 @@
         <v>0</v>
       </c>
       <c r="F468" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G468" t="n">
         <v>30</v>
@@ -18995,7 +19190,7 @@
         <v>0</v>
       </c>
       <c r="F469" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G469" t="n">
         <v>30</v>
@@ -19030,7 +19225,7 @@
         <v>0</v>
       </c>
       <c r="F470" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G470" t="n">
         <v>30</v>
@@ -19065,7 +19260,7 @@
         <v>0</v>
       </c>
       <c r="F471" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G471" t="n">
         <v>30</v>
@@ -19100,7 +19295,7 @@
         <v>0</v>
       </c>
       <c r="F472" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G472" t="n">
         <v>30</v>
@@ -19135,7 +19330,7 @@
         <v>0</v>
       </c>
       <c r="F473" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G473" t="n">
         <v>30</v>
@@ -19170,7 +19365,7 @@
         <v>0</v>
       </c>
       <c r="F474" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G474" t="n">
         <v>30</v>
@@ -19205,7 +19400,7 @@
         <v>0</v>
       </c>
       <c r="F475" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G475" t="n">
         <v>30</v>
@@ -19240,7 +19435,7 @@
         <v>0</v>
       </c>
       <c r="F476" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G476" t="n">
         <v>30</v>
@@ -19275,7 +19470,7 @@
         <v>0</v>
       </c>
       <c r="F477" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G477" t="n">
         <v>30</v>
@@ -20290,7 +20485,7 @@
         <v>1</v>
       </c>
       <c r="F506" t="n">
-        <v>0.3339691506706327</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G506" t="n">
         <v>30</v>
@@ -20325,7 +20520,7 @@
         <v>1</v>
       </c>
       <c r="F507" t="n">
-        <v>0.3339691506706327</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G507" t="n">
         <v>30</v>
@@ -20360,7 +20555,7 @@
         <v>1</v>
       </c>
       <c r="F508" t="n">
-        <v>0.3339691506706327</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G508" t="n">
         <v>30</v>
@@ -20395,7 +20590,7 @@
         <v>1</v>
       </c>
       <c r="F509" t="n">
-        <v>0.3339691506706327</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G509" t="n">
         <v>30</v>
@@ -20430,7 +20625,7 @@
         <v>1</v>
       </c>
       <c r="F510" t="n">
-        <v>0.3339691506706327</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G510" t="n">
         <v>30</v>
@@ -20465,7 +20660,7 @@
         <v>1</v>
       </c>
       <c r="F511" t="n">
-        <v>0.3339691506706327</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G511" t="n">
         <v>30</v>
@@ -20500,7 +20695,7 @@
         <v>1</v>
       </c>
       <c r="F512" t="n">
-        <v>0.3339691506706327</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G512" t="n">
         <v>30</v>
@@ -20535,7 +20730,7 @@
         <v>1</v>
       </c>
       <c r="F513" t="n">
-        <v>0.3339691506706327</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G513" t="n">
         <v>30</v>
@@ -20570,7 +20765,7 @@
         <v>1</v>
       </c>
       <c r="F514" t="n">
-        <v>0.3339691506706327</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G514" t="n">
         <v>30</v>
@@ -20605,7 +20800,7 @@
         <v>1</v>
       </c>
       <c r="F515" t="n">
-        <v>0.3339691506706327</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G515" t="n">
         <v>30</v>
@@ -20640,7 +20835,7 @@
         <v>1</v>
       </c>
       <c r="F516" t="n">
-        <v>0.3339691506706327</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G516" t="n">
         <v>30</v>
@@ -20675,7 +20870,7 @@
         <v>1</v>
       </c>
       <c r="F517" t="n">
-        <v>0.3339691506706327</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G517" t="n">
         <v>30</v>
@@ -20710,7 +20905,7 @@
         <v>1</v>
       </c>
       <c r="F518" t="n">
-        <v>0.3339691506706327</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G518" t="n">
         <v>30</v>
@@ -20745,7 +20940,7 @@
         <v>1</v>
       </c>
       <c r="F519" t="n">
-        <v>0.3339691506706327</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G519" t="n">
         <v>30</v>
@@ -20780,7 +20975,7 @@
         <v>0</v>
       </c>
       <c r="F520" t="n">
-        <v>0.7562148470837434</v>
+        <v>0.7562148470837435</v>
       </c>
       <c r="G520" t="n">
         <v>30</v>
@@ -20815,7 +21010,7 @@
         <v>0</v>
       </c>
       <c r="F521" t="n">
-        <v>0.7562148470837434</v>
+        <v>0.7562148470837435</v>
       </c>
       <c r="G521" t="n">
         <v>30</v>
@@ -20850,7 +21045,7 @@
         <v>0</v>
       </c>
       <c r="F522" t="n">
-        <v>0.7562148470837434</v>
+        <v>0.7562148470837435</v>
       </c>
       <c r="G522" t="n">
         <v>30</v>
@@ -20885,7 +21080,7 @@
         <v>0</v>
       </c>
       <c r="F523" t="n">
-        <v>0.7562148470837434</v>
+        <v>0.7562148470837435</v>
       </c>
       <c r="G523" t="n">
         <v>30</v>
@@ -20920,7 +21115,7 @@
         <v>0</v>
       </c>
       <c r="F524" t="n">
-        <v>0.7562148470837434</v>
+        <v>0.7562148470837435</v>
       </c>
       <c r="G524" t="n">
         <v>30</v>
@@ -20955,7 +21150,7 @@
         <v>0</v>
       </c>
       <c r="F525" t="n">
-        <v>0.7562148470837434</v>
+        <v>0.7562148470837435</v>
       </c>
       <c r="G525" t="n">
         <v>30</v>
@@ -20990,7 +21185,7 @@
         <v>0</v>
       </c>
       <c r="F526" t="n">
-        <v>0.7562148470837434</v>
+        <v>0.7562148470837435</v>
       </c>
       <c r="G526" t="n">
         <v>30</v>
@@ -21025,7 +21220,7 @@
         <v>0</v>
       </c>
       <c r="F527" t="n">
-        <v>0.7562148470837434</v>
+        <v>0.7562148470837435</v>
       </c>
       <c r="G527" t="n">
         <v>30</v>
@@ -21060,7 +21255,7 @@
         <v>0</v>
       </c>
       <c r="F528" t="n">
-        <v>0.7562148470837434</v>
+        <v>0.7562148470837435</v>
       </c>
       <c r="G528" t="n">
         <v>30</v>
@@ -21095,7 +21290,7 @@
         <v>0</v>
       </c>
       <c r="F529" t="n">
-        <v>0.7562148470837434</v>
+        <v>0.7562148470837435</v>
       </c>
       <c r="G529" t="n">
         <v>30</v>
@@ -21130,7 +21325,7 @@
         <v>0</v>
       </c>
       <c r="F530" t="n">
-        <v>0.7562148470837434</v>
+        <v>0.7562148470837435</v>
       </c>
       <c r="G530" t="n">
         <v>30</v>
@@ -21165,7 +21360,7 @@
         <v>0</v>
       </c>
       <c r="F531" t="n">
-        <v>0.7562148470837434</v>
+        <v>0.7562148470837435</v>
       </c>
       <c r="G531" t="n">
         <v>30</v>
@@ -21200,7 +21395,7 @@
         <v>0</v>
       </c>
       <c r="F532" t="n">
-        <v>0.7562148470837434</v>
+        <v>0.7562148470837435</v>
       </c>
       <c r="G532" t="n">
         <v>30</v>
@@ -21235,7 +21430,7 @@
         <v>0</v>
       </c>
       <c r="F533" t="n">
-        <v>0.7562148470837434</v>
+        <v>0.7562148470837435</v>
       </c>
       <c r="G533" t="n">
         <v>30</v>
@@ -21270,7 +21465,7 @@
         <v>1</v>
       </c>
       <c r="F534" t="n">
-        <v>0.309981302146957</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G534" t="n">
         <v>30</v>
@@ -21305,7 +21500,7 @@
         <v>1</v>
       </c>
       <c r="F535" t="n">
-        <v>0.309981302146957</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G535" t="n">
         <v>30</v>
@@ -21340,7 +21535,7 @@
         <v>1</v>
       </c>
       <c r="F536" t="n">
-        <v>0.309981302146957</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G536" t="n">
         <v>30</v>
@@ -21375,7 +21570,7 @@
         <v>1</v>
       </c>
       <c r="F537" t="n">
-        <v>0.309981302146957</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G537" t="n">
         <v>30</v>
@@ -21410,7 +21605,7 @@
         <v>1</v>
       </c>
       <c r="F538" t="n">
-        <v>0.309981302146957</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G538" t="n">
         <v>30</v>
@@ -21445,7 +21640,7 @@
         <v>1</v>
       </c>
       <c r="F539" t="n">
-        <v>0.309981302146957</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G539" t="n">
         <v>30</v>
@@ -21480,7 +21675,7 @@
         <v>1</v>
       </c>
       <c r="F540" t="n">
-        <v>0.309981302146957</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G540" t="n">
         <v>30</v>
@@ -21515,7 +21710,7 @@
         <v>1</v>
       </c>
       <c r="F541" t="n">
-        <v>0.309981302146957</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G541" t="n">
         <v>30</v>
@@ -21550,7 +21745,7 @@
         <v>1</v>
       </c>
       <c r="F542" t="n">
-        <v>0.309981302146957</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G542" t="n">
         <v>30</v>
@@ -21585,7 +21780,7 @@
         <v>1</v>
       </c>
       <c r="F543" t="n">
-        <v>0.309981302146957</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G543" t="n">
         <v>30</v>
@@ -21620,7 +21815,7 @@
         <v>1</v>
       </c>
       <c r="F544" t="n">
-        <v>0.309981302146957</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G544" t="n">
         <v>30</v>
@@ -21655,7 +21850,7 @@
         <v>1</v>
       </c>
       <c r="F545" t="n">
-        <v>0.309981302146957</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G545" t="n">
         <v>30</v>
@@ -21690,7 +21885,7 @@
         <v>1</v>
       </c>
       <c r="F546" t="n">
-        <v>0.309981302146957</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G546" t="n">
         <v>30</v>
@@ -21725,7 +21920,7 @@
         <v>1</v>
       </c>
       <c r="F547" t="n">
-        <v>0.309981302146957</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G547" t="n">
         <v>30</v>
@@ -21760,7 +21955,7 @@
         <v>0</v>
       </c>
       <c r="F548" t="n">
-        <v>0.6206798215778696</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G548" t="n">
         <v>30</v>
@@ -21795,7 +21990,7 @@
         <v>0</v>
       </c>
       <c r="F549" t="n">
-        <v>0.6206798215778696</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G549" t="n">
         <v>30</v>
@@ -21830,7 +22025,7 @@
         <v>0</v>
       </c>
       <c r="F550" t="n">
-        <v>0.6206798215778696</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G550" t="n">
         <v>30</v>
@@ -21865,7 +22060,7 @@
         <v>0</v>
       </c>
       <c r="F551" t="n">
-        <v>0.6206798215778696</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G551" t="n">
         <v>30</v>
@@ -21900,7 +22095,7 @@
         <v>0</v>
       </c>
       <c r="F552" t="n">
-        <v>0.6206798215778696</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G552" t="n">
         <v>30</v>
@@ -21935,7 +22130,7 @@
         <v>0</v>
       </c>
       <c r="F553" t="n">
-        <v>0.6206798215778696</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G553" t="n">
         <v>30</v>
@@ -21970,7 +22165,7 @@
         <v>0</v>
       </c>
       <c r="F554" t="n">
-        <v>0.6206798215778696</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G554" t="n">
         <v>30</v>
@@ -22005,7 +22200,7 @@
         <v>0</v>
       </c>
       <c r="F555" t="n">
-        <v>0.6206798215778696</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G555" t="n">
         <v>30</v>
@@ -22040,7 +22235,7 @@
         <v>0</v>
       </c>
       <c r="F556" t="n">
-        <v>0.6206798215778696</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G556" t="n">
         <v>30</v>
@@ -22075,7 +22270,7 @@
         <v>0</v>
       </c>
       <c r="F557" t="n">
-        <v>0.6206798215778696</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G557" t="n">
         <v>30</v>
@@ -22110,7 +22305,7 @@
         <v>0</v>
       </c>
       <c r="F558" t="n">
-        <v>0.6206798215778696</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G558" t="n">
         <v>30</v>
@@ -22145,7 +22340,7 @@
         <v>0</v>
       </c>
       <c r="F559" t="n">
-        <v>0.6206798215778696</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G559" t="n">
         <v>30</v>
@@ -22180,7 +22375,7 @@
         <v>0</v>
       </c>
       <c r="F560" t="n">
-        <v>0.6206798215778696</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G560" t="n">
         <v>30</v>
@@ -22215,7 +22410,7 @@
         <v>0</v>
       </c>
       <c r="F561" t="n">
-        <v>0.6206798215778696</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G561" t="n">
         <v>30</v>
@@ -23230,7 +23425,7 @@
         <v>1</v>
       </c>
       <c r="F590" t="n">
-        <v>0.3555211313540392</v>
+        <v>0.3555211313540388</v>
       </c>
       <c r="G590" t="n">
         <v>30</v>
@@ -23265,7 +23460,7 @@
         <v>1</v>
       </c>
       <c r="F591" t="n">
-        <v>0.3555211313540392</v>
+        <v>0.3555211313540388</v>
       </c>
       <c r="G591" t="n">
         <v>30</v>
@@ -23300,7 +23495,7 @@
         <v>1</v>
       </c>
       <c r="F592" t="n">
-        <v>0.3555211313540392</v>
+        <v>0.3555211313540388</v>
       </c>
       <c r="G592" t="n">
         <v>30</v>
@@ -23335,7 +23530,7 @@
         <v>1</v>
       </c>
       <c r="F593" t="n">
-        <v>0.3555211313540392</v>
+        <v>0.3555211313540388</v>
       </c>
       <c r="G593" t="n">
         <v>30</v>
@@ -23370,7 +23565,7 @@
         <v>1</v>
       </c>
       <c r="F594" t="n">
-        <v>0.3555211313540392</v>
+        <v>0.3555211313540388</v>
       </c>
       <c r="G594" t="n">
         <v>30</v>
@@ -23405,7 +23600,7 @@
         <v>1</v>
       </c>
       <c r="F595" t="n">
-        <v>0.3555211313540392</v>
+        <v>0.3555211313540388</v>
       </c>
       <c r="G595" t="n">
         <v>30</v>
@@ -23440,7 +23635,7 @@
         <v>1</v>
       </c>
       <c r="F596" t="n">
-        <v>0.3555211313540392</v>
+        <v>0.3555211313540388</v>
       </c>
       <c r="G596" t="n">
         <v>30</v>
@@ -23475,7 +23670,7 @@
         <v>1</v>
       </c>
       <c r="F597" t="n">
-        <v>0.3555211313540392</v>
+        <v>0.3555211313540388</v>
       </c>
       <c r="G597" t="n">
         <v>30</v>
@@ -23510,7 +23705,7 @@
         <v>1</v>
       </c>
       <c r="F598" t="n">
-        <v>0.3555211313540392</v>
+        <v>0.3555211313540388</v>
       </c>
       <c r="G598" t="n">
         <v>30</v>
@@ -23545,7 +23740,7 @@
         <v>1</v>
       </c>
       <c r="F599" t="n">
-        <v>0.3555211313540392</v>
+        <v>0.3555211313540388</v>
       </c>
       <c r="G599" t="n">
         <v>30</v>
@@ -23580,7 +23775,7 @@
         <v>1</v>
       </c>
       <c r="F600" t="n">
-        <v>0.3555211313540392</v>
+        <v>0.3555211313540388</v>
       </c>
       <c r="G600" t="n">
         <v>30</v>
@@ -23615,7 +23810,7 @@
         <v>1</v>
       </c>
       <c r="F601" t="n">
-        <v>0.3555211313540392</v>
+        <v>0.3555211313540388</v>
       </c>
       <c r="G601" t="n">
         <v>30</v>
@@ -23650,7 +23845,7 @@
         <v>1</v>
       </c>
       <c r="F602" t="n">
-        <v>0.3555211313540392</v>
+        <v>0.3555211313540388</v>
       </c>
       <c r="G602" t="n">
         <v>30</v>
@@ -23685,7 +23880,7 @@
         <v>1</v>
       </c>
       <c r="F603" t="n">
-        <v>0.3555211313540392</v>
+        <v>0.3555211313540388</v>
       </c>
       <c r="G603" t="n">
         <v>30</v>
@@ -23720,7 +23915,7 @@
         <v>0</v>
       </c>
       <c r="F604" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G604" t="n">
         <v>30</v>
@@ -23755,7 +23950,7 @@
         <v>0</v>
       </c>
       <c r="F605" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G605" t="n">
         <v>30</v>
@@ -23790,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="F606" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G606" t="n">
         <v>30</v>
@@ -23825,7 +24020,7 @@
         <v>0</v>
       </c>
       <c r="F607" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G607" t="n">
         <v>30</v>
@@ -23860,7 +24055,7 @@
         <v>0</v>
       </c>
       <c r="F608" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G608" t="n">
         <v>30</v>
@@ -23895,7 +24090,7 @@
         <v>0</v>
       </c>
       <c r="F609" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G609" t="n">
         <v>30</v>
@@ -23930,7 +24125,7 @@
         <v>0</v>
       </c>
       <c r="F610" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G610" t="n">
         <v>30</v>
@@ -23965,7 +24160,7 @@
         <v>0</v>
       </c>
       <c r="F611" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G611" t="n">
         <v>30</v>
@@ -24000,7 +24195,7 @@
         <v>0</v>
       </c>
       <c r="F612" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G612" t="n">
         <v>30</v>
@@ -24035,7 +24230,7 @@
         <v>0</v>
       </c>
       <c r="F613" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G613" t="n">
         <v>30</v>
@@ -24070,7 +24265,7 @@
         <v>0</v>
       </c>
       <c r="F614" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G614" t="n">
         <v>30</v>
@@ -24105,7 +24300,7 @@
         <v>0</v>
       </c>
       <c r="F615" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G615" t="n">
         <v>30</v>
@@ -24140,7 +24335,7 @@
         <v>0</v>
       </c>
       <c r="F616" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G616" t="n">
         <v>30</v>
@@ -24175,7 +24370,7 @@
         <v>0</v>
       </c>
       <c r="F617" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G617" t="n">
         <v>30</v>
@@ -24700,7 +24895,7 @@
         <v>0</v>
       </c>
       <c r="F632" t="n">
-        <v>0.6837634771311952</v>
+        <v>0.6837634771311956</v>
       </c>
       <c r="G632" t="n">
         <v>30</v>
@@ -24735,7 +24930,7 @@
         <v>0</v>
       </c>
       <c r="F633" t="n">
-        <v>0.6837634771311952</v>
+        <v>0.6837634771311956</v>
       </c>
       <c r="G633" t="n">
         <v>30</v>
@@ -24770,7 +24965,7 @@
         <v>0</v>
       </c>
       <c r="F634" t="n">
-        <v>0.6837634771311952</v>
+        <v>0.6837634771311956</v>
       </c>
       <c r="G634" t="n">
         <v>30</v>
@@ -24805,7 +25000,7 @@
         <v>0</v>
       </c>
       <c r="F635" t="n">
-        <v>0.6837634771311952</v>
+        <v>0.6837634771311956</v>
       </c>
       <c r="G635" t="n">
         <v>30</v>
@@ -24840,7 +25035,7 @@
         <v>0</v>
       </c>
       <c r="F636" t="n">
-        <v>0.6837634771311952</v>
+        <v>0.6837634771311956</v>
       </c>
       <c r="G636" t="n">
         <v>30</v>
@@ -24875,7 +25070,7 @@
         <v>0</v>
       </c>
       <c r="F637" t="n">
-        <v>0.6837634771311952</v>
+        <v>0.6837634771311956</v>
       </c>
       <c r="G637" t="n">
         <v>30</v>
@@ -24910,7 +25105,7 @@
         <v>0</v>
       </c>
       <c r="F638" t="n">
-        <v>0.6837634771311952</v>
+        <v>0.6837634771311956</v>
       </c>
       <c r="G638" t="n">
         <v>30</v>
@@ -24945,7 +25140,7 @@
         <v>0</v>
       </c>
       <c r="F639" t="n">
-        <v>0.6837634771311952</v>
+        <v>0.6837634771311956</v>
       </c>
       <c r="G639" t="n">
         <v>30</v>
@@ -24980,7 +25175,7 @@
         <v>0</v>
       </c>
       <c r="F640" t="n">
-        <v>0.6837634771311952</v>
+        <v>0.6837634771311956</v>
       </c>
       <c r="G640" t="n">
         <v>30</v>
@@ -25015,7 +25210,7 @@
         <v>0</v>
       </c>
       <c r="F641" t="n">
-        <v>0.6837634771311952</v>
+        <v>0.6837634771311956</v>
       </c>
       <c r="G641" t="n">
         <v>30</v>
@@ -25050,7 +25245,7 @@
         <v>0</v>
       </c>
       <c r="F642" t="n">
-        <v>0.6837634771311952</v>
+        <v>0.6837634771311956</v>
       </c>
       <c r="G642" t="n">
         <v>30</v>
@@ -25085,7 +25280,7 @@
         <v>0</v>
       </c>
       <c r="F643" t="n">
-        <v>0.6837634771311952</v>
+        <v>0.6837634771311956</v>
       </c>
       <c r="G643" t="n">
         <v>30</v>
@@ -25120,7 +25315,7 @@
         <v>0</v>
       </c>
       <c r="F644" t="n">
-        <v>0.6837634771311952</v>
+        <v>0.6837634771311956</v>
       </c>
       <c r="G644" t="n">
         <v>30</v>
@@ -25155,7 +25350,7 @@
         <v>0</v>
       </c>
       <c r="F645" t="n">
-        <v>0.6837634771311952</v>
+        <v>0.6837634771311956</v>
       </c>
       <c r="G645" t="n">
         <v>30</v>
@@ -25680,7 +25875,7 @@
         <v>0</v>
       </c>
       <c r="F660" t="n">
-        <v>0.5905033332764389</v>
+        <v>0.590503333276439</v>
       </c>
       <c r="G660" t="n">
         <v>30</v>
@@ -25715,7 +25910,7 @@
         <v>0</v>
       </c>
       <c r="F661" t="n">
-        <v>0.5905033332764389</v>
+        <v>0.590503333276439</v>
       </c>
       <c r="G661" t="n">
         <v>30</v>
@@ -25750,7 +25945,7 @@
         <v>0</v>
       </c>
       <c r="F662" t="n">
-        <v>0.5905033332764389</v>
+        <v>0.590503333276439</v>
       </c>
       <c r="G662" t="n">
         <v>30</v>
@@ -25785,7 +25980,7 @@
         <v>0</v>
       </c>
       <c r="F663" t="n">
-        <v>0.5905033332764389</v>
+        <v>0.590503333276439</v>
       </c>
       <c r="G663" t="n">
         <v>30</v>
@@ -25820,7 +26015,7 @@
         <v>0</v>
       </c>
       <c r="F664" t="n">
-        <v>0.5905033332764389</v>
+        <v>0.590503333276439</v>
       </c>
       <c r="G664" t="n">
         <v>30</v>
@@ -25855,7 +26050,7 @@
         <v>0</v>
       </c>
       <c r="F665" t="n">
-        <v>0.5905033332764389</v>
+        <v>0.590503333276439</v>
       </c>
       <c r="G665" t="n">
         <v>30</v>
@@ -25890,7 +26085,7 @@
         <v>0</v>
       </c>
       <c r="F666" t="n">
-        <v>0.5905033332764389</v>
+        <v>0.590503333276439</v>
       </c>
       <c r="G666" t="n">
         <v>30</v>
@@ -25925,7 +26120,7 @@
         <v>0</v>
       </c>
       <c r="F667" t="n">
-        <v>0.5905033332764389</v>
+        <v>0.590503333276439</v>
       </c>
       <c r="G667" t="n">
         <v>30</v>
@@ -25960,7 +26155,7 @@
         <v>0</v>
       </c>
       <c r="F668" t="n">
-        <v>0.5905033332764389</v>
+        <v>0.590503333276439</v>
       </c>
       <c r="G668" t="n">
         <v>30</v>
@@ -25995,7 +26190,7 @@
         <v>0</v>
       </c>
       <c r="F669" t="n">
-        <v>0.5905033332764389</v>
+        <v>0.590503333276439</v>
       </c>
       <c r="G669" t="n">
         <v>30</v>
@@ -26030,7 +26225,7 @@
         <v>0</v>
       </c>
       <c r="F670" t="n">
-        <v>0.5905033332764389</v>
+        <v>0.590503333276439</v>
       </c>
       <c r="G670" t="n">
         <v>30</v>
@@ -26065,7 +26260,7 @@
         <v>0</v>
       </c>
       <c r="F671" t="n">
-        <v>0.5905033332764389</v>
+        <v>0.590503333276439</v>
       </c>
       <c r="G671" t="n">
         <v>30</v>
@@ -26100,7 +26295,7 @@
         <v>0</v>
       </c>
       <c r="F672" t="n">
-        <v>0.5905033332764389</v>
+        <v>0.590503333276439</v>
       </c>
       <c r="G672" t="n">
         <v>30</v>
@@ -26135,7 +26330,7 @@
         <v>0</v>
       </c>
       <c r="F673" t="n">
-        <v>0.5905033332764389</v>
+        <v>0.590503333276439</v>
       </c>
       <c r="G673" t="n">
         <v>30</v>
@@ -26660,7 +26855,7 @@
         <v>0</v>
       </c>
       <c r="F688" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005731</v>
       </c>
       <c r="G688" t="n">
         <v>30</v>
@@ -26695,7 +26890,7 @@
         <v>0</v>
       </c>
       <c r="F689" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005731</v>
       </c>
       <c r="G689" t="n">
         <v>30</v>
@@ -26730,7 +26925,7 @@
         <v>0</v>
       </c>
       <c r="F690" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005731</v>
       </c>
       <c r="G690" t="n">
         <v>30</v>
@@ -26765,7 +26960,7 @@
         <v>0</v>
       </c>
       <c r="F691" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005731</v>
       </c>
       <c r="G691" t="n">
         <v>30</v>
@@ -26800,7 +26995,7 @@
         <v>0</v>
       </c>
       <c r="F692" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005731</v>
       </c>
       <c r="G692" t="n">
         <v>30</v>
@@ -26835,7 +27030,7 @@
         <v>0</v>
       </c>
       <c r="F693" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005731</v>
       </c>
       <c r="G693" t="n">
         <v>30</v>
@@ -26870,7 +27065,7 @@
         <v>0</v>
       </c>
       <c r="F694" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005731</v>
       </c>
       <c r="G694" t="n">
         <v>30</v>
@@ -26905,7 +27100,7 @@
         <v>0</v>
       </c>
       <c r="F695" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005731</v>
       </c>
       <c r="G695" t="n">
         <v>30</v>
@@ -26940,7 +27135,7 @@
         <v>0</v>
       </c>
       <c r="F696" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005731</v>
       </c>
       <c r="G696" t="n">
         <v>30</v>
@@ -26975,7 +27170,7 @@
         <v>0</v>
       </c>
       <c r="F697" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005731</v>
       </c>
       <c r="G697" t="n">
         <v>30</v>
@@ -27010,7 +27205,7 @@
         <v>0</v>
       </c>
       <c r="F698" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005731</v>
       </c>
       <c r="G698" t="n">
         <v>30</v>
@@ -27045,7 +27240,7 @@
         <v>0</v>
       </c>
       <c r="F699" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005731</v>
       </c>
       <c r="G699" t="n">
         <v>30</v>
@@ -27080,7 +27275,7 @@
         <v>0</v>
       </c>
       <c r="F700" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005731</v>
       </c>
       <c r="G700" t="n">
         <v>30</v>
@@ -27115,7 +27310,7 @@
         <v>0</v>
       </c>
       <c r="F701" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005731</v>
       </c>
       <c r="G701" t="n">
         <v>30</v>
@@ -27640,7 +27835,7 @@
         <v>0</v>
       </c>
       <c r="F716" t="n">
-        <v>0.7058504031720535</v>
+        <v>0.7058504031720536</v>
       </c>
       <c r="G716" t="n">
         <v>30</v>
@@ -27675,7 +27870,7 @@
         <v>0</v>
       </c>
       <c r="F717" t="n">
-        <v>0.7058504031720535</v>
+        <v>0.7058504031720536</v>
       </c>
       <c r="G717" t="n">
         <v>30</v>
@@ -27710,7 +27905,7 @@
         <v>0</v>
       </c>
       <c r="F718" t="n">
-        <v>0.7058504031720535</v>
+        <v>0.7058504031720536</v>
       </c>
       <c r="G718" t="n">
         <v>30</v>
@@ -27745,7 +27940,7 @@
         <v>0</v>
       </c>
       <c r="F719" t="n">
-        <v>0.7058504031720535</v>
+        <v>0.7058504031720536</v>
       </c>
       <c r="G719" t="n">
         <v>30</v>
@@ -27780,7 +27975,7 @@
         <v>0</v>
       </c>
       <c r="F720" t="n">
-        <v>0.7058504031720535</v>
+        <v>0.7058504031720536</v>
       </c>
       <c r="G720" t="n">
         <v>30</v>
@@ -27815,7 +28010,7 @@
         <v>0</v>
       </c>
       <c r="F721" t="n">
-        <v>0.7058504031720535</v>
+        <v>0.7058504031720536</v>
       </c>
       <c r="G721" t="n">
         <v>30</v>
@@ -27850,7 +28045,7 @@
         <v>0</v>
       </c>
       <c r="F722" t="n">
-        <v>0.7058504031720535</v>
+        <v>0.7058504031720536</v>
       </c>
       <c r="G722" t="n">
         <v>30</v>
@@ -27885,7 +28080,7 @@
         <v>0</v>
       </c>
       <c r="F723" t="n">
-        <v>0.7058504031720535</v>
+        <v>0.7058504031720536</v>
       </c>
       <c r="G723" t="n">
         <v>30</v>
@@ -27920,7 +28115,7 @@
         <v>0</v>
       </c>
       <c r="F724" t="n">
-        <v>0.7058504031720535</v>
+        <v>0.7058504031720536</v>
       </c>
       <c r="G724" t="n">
         <v>30</v>
@@ -27955,7 +28150,7 @@
         <v>0</v>
       </c>
       <c r="F725" t="n">
-        <v>0.7058504031720535</v>
+        <v>0.7058504031720536</v>
       </c>
       <c r="G725" t="n">
         <v>30</v>
@@ -27990,7 +28185,7 @@
         <v>0</v>
       </c>
       <c r="F726" t="n">
-        <v>0.7058504031720535</v>
+        <v>0.7058504031720536</v>
       </c>
       <c r="G726" t="n">
         <v>30</v>
@@ -28025,7 +28220,7 @@
         <v>0</v>
       </c>
       <c r="F727" t="n">
-        <v>0.7058504031720535</v>
+        <v>0.7058504031720536</v>
       </c>
       <c r="G727" t="n">
         <v>30</v>
@@ -28060,7 +28255,7 @@
         <v>0</v>
       </c>
       <c r="F728" t="n">
-        <v>0.7058504031720535</v>
+        <v>0.7058504031720536</v>
       </c>
       <c r="G728" t="n">
         <v>30</v>
@@ -28095,7 +28290,7 @@
         <v>0</v>
       </c>
       <c r="F729" t="n">
-        <v>0.7058504031720535</v>
+        <v>0.7058504031720536</v>
       </c>
       <c r="G729" t="n">
         <v>30</v>
@@ -28130,7 +28325,7 @@
         <v>1</v>
       </c>
       <c r="F730" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G730" t="n">
         <v>30</v>
@@ -28165,7 +28360,7 @@
         <v>1</v>
       </c>
       <c r="F731" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G731" t="n">
         <v>30</v>
@@ -28200,7 +28395,7 @@
         <v>1</v>
       </c>
       <c r="F732" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G732" t="n">
         <v>30</v>
@@ -28235,7 +28430,7 @@
         <v>1</v>
       </c>
       <c r="F733" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G733" t="n">
         <v>30</v>
@@ -28270,7 +28465,7 @@
         <v>1</v>
       </c>
       <c r="F734" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G734" t="n">
         <v>30</v>
@@ -28305,7 +28500,7 @@
         <v>1</v>
       </c>
       <c r="F735" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G735" t="n">
         <v>30</v>
@@ -28340,7 +28535,7 @@
         <v>1</v>
       </c>
       <c r="F736" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G736" t="n">
         <v>30</v>
@@ -28375,7 +28570,7 @@
         <v>1</v>
       </c>
       <c r="F737" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G737" t="n">
         <v>30</v>
@@ -28410,7 +28605,7 @@
         <v>1</v>
       </c>
       <c r="F738" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G738" t="n">
         <v>30</v>
@@ -28445,7 +28640,7 @@
         <v>1</v>
       </c>
       <c r="F739" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G739" t="n">
         <v>30</v>
@@ -28480,7 +28675,7 @@
         <v>1</v>
       </c>
       <c r="F740" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G740" t="n">
         <v>30</v>
@@ -28515,7 +28710,7 @@
         <v>1</v>
       </c>
       <c r="F741" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G741" t="n">
         <v>30</v>
@@ -28550,7 +28745,7 @@
         <v>1</v>
       </c>
       <c r="F742" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G742" t="n">
         <v>30</v>
@@ -28585,7 +28780,7 @@
         <v>1</v>
       </c>
       <c r="F743" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G743" t="n">
         <v>30</v>
@@ -28620,7 +28815,7 @@
         <v>0</v>
       </c>
       <c r="F744" t="n">
-        <v>0.6281397714709056</v>
+        <v>0.6281397714709055</v>
       </c>
       <c r="G744" t="n">
         <v>30</v>
@@ -28655,7 +28850,7 @@
         <v>0</v>
       </c>
       <c r="F745" t="n">
-        <v>0.6281397714709056</v>
+        <v>0.6281397714709055</v>
       </c>
       <c r="G745" t="n">
         <v>30</v>
@@ -28690,7 +28885,7 @@
         <v>0</v>
       </c>
       <c r="F746" t="n">
-        <v>0.6281397714709056</v>
+        <v>0.6281397714709055</v>
       </c>
       <c r="G746" t="n">
         <v>30</v>
@@ -28725,7 +28920,7 @@
         <v>0</v>
       </c>
       <c r="F747" t="n">
-        <v>0.6281397714709056</v>
+        <v>0.6281397714709055</v>
       </c>
       <c r="G747" t="n">
         <v>30</v>
@@ -28760,7 +28955,7 @@
         <v>0</v>
       </c>
       <c r="F748" t="n">
-        <v>0.6281397714709056</v>
+        <v>0.6281397714709055</v>
       </c>
       <c r="G748" t="n">
         <v>30</v>
@@ -28795,7 +28990,7 @@
         <v>0</v>
       </c>
       <c r="F749" t="n">
-        <v>0.6281397714709056</v>
+        <v>0.6281397714709055</v>
       </c>
       <c r="G749" t="n">
         <v>30</v>
@@ -28830,7 +29025,7 @@
         <v>0</v>
       </c>
       <c r="F750" t="n">
-        <v>0.6281397714709056</v>
+        <v>0.6281397714709055</v>
       </c>
       <c r="G750" t="n">
         <v>30</v>
@@ -28865,7 +29060,7 @@
         <v>0</v>
       </c>
       <c r="F751" t="n">
-        <v>0.6281397714709056</v>
+        <v>0.6281397714709055</v>
       </c>
       <c r="G751" t="n">
         <v>30</v>
@@ -28900,7 +29095,7 @@
         <v>0</v>
       </c>
       <c r="F752" t="n">
-        <v>0.6281397714709056</v>
+        <v>0.6281397714709055</v>
       </c>
       <c r="G752" t="n">
         <v>30</v>
@@ -28935,7 +29130,7 @@
         <v>0</v>
       </c>
       <c r="F753" t="n">
-        <v>0.6281397714709056</v>
+        <v>0.6281397714709055</v>
       </c>
       <c r="G753" t="n">
         <v>30</v>
@@ -28970,7 +29165,7 @@
         <v>0</v>
       </c>
       <c r="F754" t="n">
-        <v>0.6281397714709056</v>
+        <v>0.6281397714709055</v>
       </c>
       <c r="G754" t="n">
         <v>30</v>
@@ -29005,7 +29200,7 @@
         <v>0</v>
       </c>
       <c r="F755" t="n">
-        <v>0.6281397714709056</v>
+        <v>0.6281397714709055</v>
       </c>
       <c r="G755" t="n">
         <v>30</v>
@@ -29040,7 +29235,7 @@
         <v>0</v>
       </c>
       <c r="F756" t="n">
-        <v>0.6281397714709056</v>
+        <v>0.6281397714709055</v>
       </c>
       <c r="G756" t="n">
         <v>30</v>
@@ -29075,7 +29270,7 @@
         <v>0</v>
       </c>
       <c r="F757" t="n">
-        <v>0.6281397714709056</v>
+        <v>0.6281397714709055</v>
       </c>
       <c r="G757" t="n">
         <v>30</v>
@@ -29110,7 +29305,7 @@
         <v>1</v>
       </c>
       <c r="F758" t="n">
-        <v>0.6171259152308187</v>
+        <v>0.6171259152308185</v>
       </c>
       <c r="G758" t="n">
         <v>30</v>
@@ -29145,7 +29340,7 @@
         <v>1</v>
       </c>
       <c r="F759" t="n">
-        <v>0.6171259152308187</v>
+        <v>0.6171259152308185</v>
       </c>
       <c r="G759" t="n">
         <v>30</v>
@@ -29180,7 +29375,7 @@
         <v>1</v>
       </c>
       <c r="F760" t="n">
-        <v>0.6171259152308187</v>
+        <v>0.6171259152308185</v>
       </c>
       <c r="G760" t="n">
         <v>30</v>
@@ -29215,7 +29410,7 @@
         <v>1</v>
       </c>
       <c r="F761" t="n">
-        <v>0.6171259152308187</v>
+        <v>0.6171259152308185</v>
       </c>
       <c r="G761" t="n">
         <v>30</v>
@@ -29250,7 +29445,7 @@
         <v>1</v>
       </c>
       <c r="F762" t="n">
-        <v>0.6171259152308187</v>
+        <v>0.6171259152308185</v>
       </c>
       <c r="G762" t="n">
         <v>30</v>
@@ -29285,7 +29480,7 @@
         <v>1</v>
       </c>
       <c r="F763" t="n">
-        <v>0.6171259152308187</v>
+        <v>0.6171259152308185</v>
       </c>
       <c r="G763" t="n">
         <v>30</v>
@@ -29320,7 +29515,7 @@
         <v>1</v>
       </c>
       <c r="F764" t="n">
-        <v>0.6171259152308187</v>
+        <v>0.6171259152308185</v>
       </c>
       <c r="G764" t="n">
         <v>30</v>
@@ -29355,7 +29550,7 @@
         <v>1</v>
       </c>
       <c r="F765" t="n">
-        <v>0.6171259152308187</v>
+        <v>0.6171259152308185</v>
       </c>
       <c r="G765" t="n">
         <v>30</v>
@@ -29390,7 +29585,7 @@
         <v>1</v>
       </c>
       <c r="F766" t="n">
-        <v>0.6171259152308187</v>
+        <v>0.6171259152308185</v>
       </c>
       <c r="G766" t="n">
         <v>30</v>
@@ -29425,7 +29620,7 @@
         <v>1</v>
       </c>
       <c r="F767" t="n">
-        <v>0.6171259152308187</v>
+        <v>0.6171259152308185</v>
       </c>
       <c r="G767" t="n">
         <v>30</v>
@@ -29460,7 +29655,7 @@
         <v>1</v>
       </c>
       <c r="F768" t="n">
-        <v>0.6171259152308187</v>
+        <v>0.6171259152308185</v>
       </c>
       <c r="G768" t="n">
         <v>30</v>
@@ -29495,7 +29690,7 @@
         <v>1</v>
       </c>
       <c r="F769" t="n">
-        <v>0.6171259152308187</v>
+        <v>0.6171259152308185</v>
       </c>
       <c r="G769" t="n">
         <v>30</v>
@@ -29530,7 +29725,7 @@
         <v>1</v>
       </c>
       <c r="F770" t="n">
-        <v>0.6171259152308187</v>
+        <v>0.6171259152308185</v>
       </c>
       <c r="G770" t="n">
         <v>30</v>
@@ -29565,7 +29760,7 @@
         <v>1</v>
       </c>
       <c r="F771" t="n">
-        <v>0.6171259152308187</v>
+        <v>0.6171259152308185</v>
       </c>
       <c r="G771" t="n">
         <v>30</v>
@@ -31560,7 +31755,7 @@
         <v>0</v>
       </c>
       <c r="F828" t="n">
-        <v>0.7097832071010935</v>
+        <v>0.709783207101094</v>
       </c>
       <c r="G828" t="n">
         <v>30</v>
@@ -31595,7 +31790,7 @@
         <v>0</v>
       </c>
       <c r="F829" t="n">
-        <v>0.7097832071010935</v>
+        <v>0.709783207101094</v>
       </c>
       <c r="G829" t="n">
         <v>30</v>
@@ -31630,7 +31825,7 @@
         <v>0</v>
       </c>
       <c r="F830" t="n">
-        <v>0.7097832071010935</v>
+        <v>0.709783207101094</v>
       </c>
       <c r="G830" t="n">
         <v>30</v>
@@ -31665,7 +31860,7 @@
         <v>0</v>
       </c>
       <c r="F831" t="n">
-        <v>0.7097832071010935</v>
+        <v>0.709783207101094</v>
       </c>
       <c r="G831" t="n">
         <v>30</v>
@@ -31700,7 +31895,7 @@
         <v>0</v>
       </c>
       <c r="F832" t="n">
-        <v>0.7097832071010935</v>
+        <v>0.709783207101094</v>
       </c>
       <c r="G832" t="n">
         <v>30</v>
@@ -31735,7 +31930,7 @@
         <v>0</v>
       </c>
       <c r="F833" t="n">
-        <v>0.7097832071010935</v>
+        <v>0.709783207101094</v>
       </c>
       <c r="G833" t="n">
         <v>30</v>
@@ -31770,7 +31965,7 @@
         <v>0</v>
       </c>
       <c r="F834" t="n">
-        <v>0.7097832071010935</v>
+        <v>0.709783207101094</v>
       </c>
       <c r="G834" t="n">
         <v>30</v>
@@ -31805,7 +32000,7 @@
         <v>0</v>
       </c>
       <c r="F835" t="n">
-        <v>0.7097832071010935</v>
+        <v>0.709783207101094</v>
       </c>
       <c r="G835" t="n">
         <v>30</v>
@@ -31840,7 +32035,7 @@
         <v>0</v>
       </c>
       <c r="F836" t="n">
-        <v>0.7097832071010935</v>
+        <v>0.709783207101094</v>
       </c>
       <c r="G836" t="n">
         <v>30</v>
@@ -31875,7 +32070,7 @@
         <v>0</v>
       </c>
       <c r="F837" t="n">
-        <v>0.7097832071010935</v>
+        <v>0.709783207101094</v>
       </c>
       <c r="G837" t="n">
         <v>30</v>
@@ -31910,7 +32105,7 @@
         <v>0</v>
       </c>
       <c r="F838" t="n">
-        <v>0.7097832071010935</v>
+        <v>0.709783207101094</v>
       </c>
       <c r="G838" t="n">
         <v>30</v>
@@ -31945,7 +32140,7 @@
         <v>0</v>
       </c>
       <c r="F839" t="n">
-        <v>0.7097832071010935</v>
+        <v>0.709783207101094</v>
       </c>
       <c r="G839" t="n">
         <v>30</v>
@@ -31980,7 +32175,7 @@
         <v>0</v>
       </c>
       <c r="F840" t="n">
-        <v>0.7097832071010935</v>
+        <v>0.709783207101094</v>
       </c>
       <c r="G840" t="n">
         <v>30</v>
@@ -32015,7 +32210,7 @@
         <v>0</v>
       </c>
       <c r="F841" t="n">
-        <v>0.7097832071010935</v>
+        <v>0.709783207101094</v>
       </c>
       <c r="G841" t="n">
         <v>30</v>
@@ -32540,7 +32735,7 @@
         <v>0</v>
       </c>
       <c r="F856" t="n">
-        <v>0.6369988331447253</v>
+        <v>0.6369988331447254</v>
       </c>
       <c r="G856" t="n">
         <v>30</v>
@@ -32575,7 +32770,7 @@
         <v>0</v>
       </c>
       <c r="F857" t="n">
-        <v>0.6369988331447253</v>
+        <v>0.6369988331447254</v>
       </c>
       <c r="G857" t="n">
         <v>30</v>
@@ -32610,7 +32805,7 @@
         <v>0</v>
       </c>
       <c r="F858" t="n">
-        <v>0.6369988331447253</v>
+        <v>0.6369988331447254</v>
       </c>
       <c r="G858" t="n">
         <v>30</v>
@@ -32645,7 +32840,7 @@
         <v>0</v>
       </c>
       <c r="F859" t="n">
-        <v>0.6369988331447253</v>
+        <v>0.6369988331447254</v>
       </c>
       <c r="G859" t="n">
         <v>30</v>
@@ -32680,7 +32875,7 @@
         <v>0</v>
       </c>
       <c r="F860" t="n">
-        <v>0.6369988331447253</v>
+        <v>0.6369988331447254</v>
       </c>
       <c r="G860" t="n">
         <v>30</v>
@@ -32715,7 +32910,7 @@
         <v>0</v>
       </c>
       <c r="F861" t="n">
-        <v>0.6369988331447253</v>
+        <v>0.6369988331447254</v>
       </c>
       <c r="G861" t="n">
         <v>30</v>
@@ -32750,7 +32945,7 @@
         <v>0</v>
       </c>
       <c r="F862" t="n">
-        <v>0.6369988331447253</v>
+        <v>0.6369988331447254</v>
       </c>
       <c r="G862" t="n">
         <v>30</v>
@@ -32785,7 +32980,7 @@
         <v>0</v>
       </c>
       <c r="F863" t="n">
-        <v>0.6369988331447253</v>
+        <v>0.6369988331447254</v>
       </c>
       <c r="G863" t="n">
         <v>30</v>
@@ -32820,7 +33015,7 @@
         <v>0</v>
       </c>
       <c r="F864" t="n">
-        <v>0.6369988331447253</v>
+        <v>0.6369988331447254</v>
       </c>
       <c r="G864" t="n">
         <v>30</v>
@@ -32855,7 +33050,7 @@
         <v>0</v>
       </c>
       <c r="F865" t="n">
-        <v>0.6369988331447253</v>
+        <v>0.6369988331447254</v>
       </c>
       <c r="G865" t="n">
         <v>30</v>
@@ -32890,7 +33085,7 @@
         <v>0</v>
       </c>
       <c r="F866" t="n">
-        <v>0.6369988331447253</v>
+        <v>0.6369988331447254</v>
       </c>
       <c r="G866" t="n">
         <v>30</v>
@@ -32925,7 +33120,7 @@
         <v>0</v>
       </c>
       <c r="F867" t="n">
-        <v>0.6369988331447253</v>
+        <v>0.6369988331447254</v>
       </c>
       <c r="G867" t="n">
         <v>30</v>
@@ -32960,7 +33155,7 @@
         <v>0</v>
       </c>
       <c r="F868" t="n">
-        <v>0.6369988331447253</v>
+        <v>0.6369988331447254</v>
       </c>
       <c r="G868" t="n">
         <v>30</v>
@@ -32995,7 +33190,7 @@
         <v>0</v>
       </c>
       <c r="F869" t="n">
-        <v>0.6369988331447253</v>
+        <v>0.6369988331447254</v>
       </c>
       <c r="G869" t="n">
         <v>30</v>
@@ -33030,7 +33225,7 @@
         <v>1</v>
       </c>
       <c r="F870" t="n">
-        <v>0.3166167335403822</v>
+        <v>0.3166167335403818</v>
       </c>
       <c r="G870" t="n">
         <v>30</v>
@@ -33065,7 +33260,7 @@
         <v>1</v>
       </c>
       <c r="F871" t="n">
-        <v>0.3166167335403822</v>
+        <v>0.3166167335403818</v>
       </c>
       <c r="G871" t="n">
         <v>30</v>
@@ -33100,7 +33295,7 @@
         <v>1</v>
       </c>
       <c r="F872" t="n">
-        <v>0.3166167335403822</v>
+        <v>0.3166167335403818</v>
       </c>
       <c r="G872" t="n">
         <v>30</v>
@@ -33135,7 +33330,7 @@
         <v>1</v>
       </c>
       <c r="F873" t="n">
-        <v>0.3166167335403822</v>
+        <v>0.3166167335403818</v>
       </c>
       <c r="G873" t="n">
         <v>30</v>
@@ -33170,7 +33365,7 @@
         <v>1</v>
       </c>
       <c r="F874" t="n">
-        <v>0.3166167335403822</v>
+        <v>0.3166167335403818</v>
       </c>
       <c r="G874" t="n">
         <v>30</v>
@@ -33205,7 +33400,7 @@
         <v>1</v>
       </c>
       <c r="F875" t="n">
-        <v>0.3166167335403822</v>
+        <v>0.3166167335403818</v>
       </c>
       <c r="G875" t="n">
         <v>30</v>
@@ -33240,7 +33435,7 @@
         <v>1</v>
       </c>
       <c r="F876" t="n">
-        <v>0.3166167335403822</v>
+        <v>0.3166167335403818</v>
       </c>
       <c r="G876" t="n">
         <v>30</v>
@@ -33275,7 +33470,7 @@
         <v>1</v>
       </c>
       <c r="F877" t="n">
-        <v>0.3166167335403822</v>
+        <v>0.3166167335403818</v>
       </c>
       <c r="G877" t="n">
         <v>30</v>
@@ -33310,7 +33505,7 @@
         <v>1</v>
       </c>
       <c r="F878" t="n">
-        <v>0.3166167335403822</v>
+        <v>0.3166167335403818</v>
       </c>
       <c r="G878" t="n">
         <v>30</v>
@@ -33345,7 +33540,7 @@
         <v>1</v>
       </c>
       <c r="F879" t="n">
-        <v>0.3166167335403822</v>
+        <v>0.3166167335403818</v>
       </c>
       <c r="G879" t="n">
         <v>30</v>
@@ -33380,7 +33575,7 @@
         <v>1</v>
       </c>
       <c r="F880" t="n">
-        <v>0.3166167335403822</v>
+        <v>0.3166167335403818</v>
       </c>
       <c r="G880" t="n">
         <v>30</v>
@@ -33415,7 +33610,7 @@
         <v>1</v>
       </c>
       <c r="F881" t="n">
-        <v>0.3166167335403822</v>
+        <v>0.3166167335403818</v>
       </c>
       <c r="G881" t="n">
         <v>30</v>
@@ -33450,7 +33645,7 @@
         <v>1</v>
       </c>
       <c r="F882" t="n">
-        <v>0.3166167335403822</v>
+        <v>0.3166167335403818</v>
       </c>
       <c r="G882" t="n">
         <v>30</v>
@@ -33485,7 +33680,7 @@
         <v>1</v>
       </c>
       <c r="F883" t="n">
-        <v>0.3166167335403822</v>
+        <v>0.3166167335403818</v>
       </c>
       <c r="G883" t="n">
         <v>30</v>
@@ -34500,7 +34695,7 @@
         <v>0</v>
       </c>
       <c r="F912" t="n">
-        <v>0.5585539401849067</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G912" t="n">
         <v>30</v>
@@ -34535,7 +34730,7 @@
         <v>0</v>
       </c>
       <c r="F913" t="n">
-        <v>0.5585539401849067</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G913" t="n">
         <v>30</v>
@@ -34570,7 +34765,7 @@
         <v>0</v>
       </c>
       <c r="F914" t="n">
-        <v>0.5585539401849067</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G914" t="n">
         <v>30</v>
@@ -34605,7 +34800,7 @@
         <v>0</v>
       </c>
       <c r="F915" t="n">
-        <v>0.5585539401849067</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G915" t="n">
         <v>30</v>
@@ -34640,7 +34835,7 @@
         <v>0</v>
       </c>
       <c r="F916" t="n">
-        <v>0.5585539401849067</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G916" t="n">
         <v>30</v>
@@ -34675,7 +34870,7 @@
         <v>0</v>
       </c>
       <c r="F917" t="n">
-        <v>0.5585539401849067</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G917" t="n">
         <v>30</v>
@@ -34710,7 +34905,7 @@
         <v>0</v>
       </c>
       <c r="F918" t="n">
-        <v>0.5585539401849067</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G918" t="n">
         <v>30</v>
@@ -34745,7 +34940,7 @@
         <v>0</v>
       </c>
       <c r="F919" t="n">
-        <v>0.5585539401849067</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G919" t="n">
         <v>30</v>
@@ -34780,7 +34975,7 @@
         <v>0</v>
       </c>
       <c r="F920" t="n">
-        <v>0.5585539401849067</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G920" t="n">
         <v>30</v>
@@ -34815,7 +35010,7 @@
         <v>0</v>
       </c>
       <c r="F921" t="n">
-        <v>0.5585539401849067</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G921" t="n">
         <v>30</v>
@@ -34850,7 +35045,7 @@
         <v>0</v>
       </c>
       <c r="F922" t="n">
-        <v>0.5585539401849067</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G922" t="n">
         <v>30</v>
@@ -34885,7 +35080,7 @@
         <v>0</v>
       </c>
       <c r="F923" t="n">
-        <v>0.5585539401849067</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G923" t="n">
         <v>30</v>
@@ -34920,7 +35115,7 @@
         <v>0</v>
       </c>
       <c r="F924" t="n">
-        <v>0.5585539401849067</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G924" t="n">
         <v>30</v>
@@ -34955,7 +35150,7 @@
         <v>0</v>
       </c>
       <c r="F925" t="n">
-        <v>0.5585539401849067</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G925" t="n">
         <v>30</v>
@@ -35970,7 +36165,7 @@
         <v>1</v>
       </c>
       <c r="F954" t="n">
-        <v>0.5984324623317754</v>
+        <v>0.5984324623317749</v>
       </c>
       <c r="G954" t="n">
         <v>30</v>
@@ -36005,7 +36200,7 @@
         <v>1</v>
       </c>
       <c r="F955" t="n">
-        <v>0.5984324623317754</v>
+        <v>0.5984324623317749</v>
       </c>
       <c r="G955" t="n">
         <v>30</v>
@@ -36040,7 +36235,7 @@
         <v>1</v>
       </c>
       <c r="F956" t="n">
-        <v>0.5984324623317754</v>
+        <v>0.5984324623317749</v>
       </c>
       <c r="G956" t="n">
         <v>30</v>
@@ -36075,7 +36270,7 @@
         <v>1</v>
       </c>
       <c r="F957" t="n">
-        <v>0.5984324623317754</v>
+        <v>0.5984324623317749</v>
       </c>
       <c r="G957" t="n">
         <v>30</v>
@@ -36110,7 +36305,7 @@
         <v>1</v>
       </c>
       <c r="F958" t="n">
-        <v>0.5984324623317754</v>
+        <v>0.5984324623317749</v>
       </c>
       <c r="G958" t="n">
         <v>30</v>
@@ -36145,7 +36340,7 @@
         <v>1</v>
       </c>
       <c r="F959" t="n">
-        <v>0.5984324623317754</v>
+        <v>0.5984324623317749</v>
       </c>
       <c r="G959" t="n">
         <v>30</v>
@@ -36180,7 +36375,7 @@
         <v>1</v>
       </c>
       <c r="F960" t="n">
-        <v>0.5984324623317754</v>
+        <v>0.5984324623317749</v>
       </c>
       <c r="G960" t="n">
         <v>30</v>
@@ -36215,7 +36410,7 @@
         <v>1</v>
       </c>
       <c r="F961" t="n">
-        <v>0.5984324623317754</v>
+        <v>0.5984324623317749</v>
       </c>
       <c r="G961" t="n">
         <v>30</v>
@@ -36250,7 +36445,7 @@
         <v>1</v>
       </c>
       <c r="F962" t="n">
-        <v>0.5984324623317754</v>
+        <v>0.5984324623317749</v>
       </c>
       <c r="G962" t="n">
         <v>30</v>
@@ -36285,7 +36480,7 @@
         <v>1</v>
       </c>
       <c r="F963" t="n">
-        <v>0.5984324623317754</v>
+        <v>0.5984324623317749</v>
       </c>
       <c r="G963" t="n">
         <v>30</v>
@@ -36320,7 +36515,7 @@
         <v>1</v>
       </c>
       <c r="F964" t="n">
-        <v>0.5984324623317754</v>
+        <v>0.5984324623317749</v>
       </c>
       <c r="G964" t="n">
         <v>30</v>
@@ -36355,7 +36550,7 @@
         <v>1</v>
       </c>
       <c r="F965" t="n">
-        <v>0.5984324623317754</v>
+        <v>0.5984324623317749</v>
       </c>
       <c r="G965" t="n">
         <v>30</v>
@@ -36390,7 +36585,7 @@
         <v>1</v>
       </c>
       <c r="F966" t="n">
-        <v>0.5984324623317754</v>
+        <v>0.5984324623317749</v>
       </c>
       <c r="G966" t="n">
         <v>30</v>
@@ -36425,7 +36620,7 @@
         <v>1</v>
       </c>
       <c r="F967" t="n">
-        <v>0.5984324623317754</v>
+        <v>0.5984324623317749</v>
       </c>
       <c r="G967" t="n">
         <v>30</v>
@@ -38910,7 +39105,7 @@
         <v>1</v>
       </c>
       <c r="F1038" t="n">
-        <v>0.5330511750585764</v>
+        <v>0.5330511750585766</v>
       </c>
       <c r="G1038" t="n">
         <v>30</v>
@@ -38945,7 +39140,7 @@
         <v>1</v>
       </c>
       <c r="F1039" t="n">
-        <v>0.5330511750585764</v>
+        <v>0.5330511750585766</v>
       </c>
       <c r="G1039" t="n">
         <v>30</v>
@@ -38980,7 +39175,7 @@
         <v>1</v>
       </c>
       <c r="F1040" t="n">
-        <v>0.5330511750585764</v>
+        <v>0.5330511750585766</v>
       </c>
       <c r="G1040" t="n">
         <v>30</v>
@@ -39015,7 +39210,7 @@
         <v>1</v>
       </c>
       <c r="F1041" t="n">
-        <v>0.5330511750585764</v>
+        <v>0.5330511750585766</v>
       </c>
       <c r="G1041" t="n">
         <v>30</v>
@@ -39050,7 +39245,7 @@
         <v>1</v>
       </c>
       <c r="F1042" t="n">
-        <v>0.5330511750585764</v>
+        <v>0.5330511750585766</v>
       </c>
       <c r="G1042" t="n">
         <v>30</v>
@@ -39085,7 +39280,7 @@
         <v>1</v>
       </c>
       <c r="F1043" t="n">
-        <v>0.5330511750585764</v>
+        <v>0.5330511750585766</v>
       </c>
       <c r="G1043" t="n">
         <v>30</v>
@@ -39120,7 +39315,7 @@
         <v>1</v>
       </c>
       <c r="F1044" t="n">
-        <v>0.5330511750585764</v>
+        <v>0.5330511750585766</v>
       </c>
       <c r="G1044" t="n">
         <v>30</v>
@@ -39155,7 +39350,7 @@
         <v>1</v>
       </c>
       <c r="F1045" t="n">
-        <v>0.5330511750585764</v>
+        <v>0.5330511750585766</v>
       </c>
       <c r="G1045" t="n">
         <v>30</v>
@@ -39190,7 +39385,7 @@
         <v>1</v>
       </c>
       <c r="F1046" t="n">
-        <v>0.5330511750585764</v>
+        <v>0.5330511750585766</v>
       </c>
       <c r="G1046" t="n">
         <v>30</v>
@@ -39225,7 +39420,7 @@
         <v>1</v>
       </c>
       <c r="F1047" t="n">
-        <v>0.5330511750585764</v>
+        <v>0.5330511750585766</v>
       </c>
       <c r="G1047" t="n">
         <v>30</v>
@@ -39260,7 +39455,7 @@
         <v>1</v>
       </c>
       <c r="F1048" t="n">
-        <v>0.5330511750585764</v>
+        <v>0.5330511750585766</v>
       </c>
       <c r="G1048" t="n">
         <v>30</v>
@@ -39295,7 +39490,7 @@
         <v>1</v>
       </c>
       <c r="F1049" t="n">
-        <v>0.5330511750585764</v>
+        <v>0.5330511750585766</v>
       </c>
       <c r="G1049" t="n">
         <v>30</v>
@@ -39330,7 +39525,7 @@
         <v>1</v>
       </c>
       <c r="F1050" t="n">
-        <v>0.5330511750585764</v>
+        <v>0.5330511750585766</v>
       </c>
       <c r="G1050" t="n">
         <v>30</v>
@@ -39365,7 +39560,7 @@
         <v>1</v>
       </c>
       <c r="F1051" t="n">
-        <v>0.5330511750585764</v>
+        <v>0.5330511750585766</v>
       </c>
       <c r="G1051" t="n">
         <v>30</v>
@@ -41360,7 +41555,7 @@
         <v>3</v>
       </c>
       <c r="F1108" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1108" t="n">
         <v>30</v>
@@ -41395,7 +41590,7 @@
         <v>3</v>
       </c>
       <c r="F1109" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1109" t="n">
         <v>30</v>
@@ -41430,7 +41625,7 @@
         <v>3</v>
       </c>
       <c r="F1110" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1110" t="n">
         <v>30</v>
@@ -41465,7 +41660,7 @@
         <v>3</v>
       </c>
       <c r="F1111" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1111" t="n">
         <v>30</v>
@@ -41500,7 +41695,7 @@
         <v>3</v>
       </c>
       <c r="F1112" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1112" t="n">
         <v>30</v>
@@ -41535,7 +41730,7 @@
         <v>3</v>
       </c>
       <c r="F1113" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1113" t="n">
         <v>30</v>
@@ -41570,7 +41765,7 @@
         <v>3</v>
       </c>
       <c r="F1114" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1114" t="n">
         <v>30</v>
@@ -41605,7 +41800,7 @@
         <v>3</v>
       </c>
       <c r="F1115" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1115" t="n">
         <v>30</v>
@@ -41640,7 +41835,7 @@
         <v>3</v>
       </c>
       <c r="F1116" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1116" t="n">
         <v>30</v>
@@ -41675,7 +41870,7 @@
         <v>3</v>
       </c>
       <c r="F1117" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1117" t="n">
         <v>30</v>
@@ -41710,7 +41905,7 @@
         <v>3</v>
       </c>
       <c r="F1118" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1118" t="n">
         <v>30</v>
@@ -41745,7 +41940,7 @@
         <v>3</v>
       </c>
       <c r="F1119" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1119" t="n">
         <v>30</v>
@@ -41780,7 +41975,7 @@
         <v>3</v>
       </c>
       <c r="F1120" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1120" t="n">
         <v>30</v>
@@ -41815,7 +42010,7 @@
         <v>3</v>
       </c>
       <c r="F1121" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1121" t="n">
         <v>30</v>
@@ -42340,7 +42535,7 @@
         <v>3</v>
       </c>
       <c r="F1136" t="n">
-        <v>0.3912031644641525</v>
+        <v>0.391203164464152</v>
       </c>
       <c r="G1136" t="n">
         <v>30</v>
@@ -42375,7 +42570,7 @@
         <v>3</v>
       </c>
       <c r="F1137" t="n">
-        <v>0.3912031644641525</v>
+        <v>0.391203164464152</v>
       </c>
       <c r="G1137" t="n">
         <v>30</v>
@@ -42410,7 +42605,7 @@
         <v>3</v>
       </c>
       <c r="F1138" t="n">
-        <v>0.3912031644641525</v>
+        <v>0.391203164464152</v>
       </c>
       <c r="G1138" t="n">
         <v>30</v>
@@ -42445,7 +42640,7 @@
         <v>3</v>
       </c>
       <c r="F1139" t="n">
-        <v>0.3912031644641525</v>
+        <v>0.391203164464152</v>
       </c>
       <c r="G1139" t="n">
         <v>30</v>
@@ -42480,7 +42675,7 @@
         <v>3</v>
       </c>
       <c r="F1140" t="n">
-        <v>0.3912031644641525</v>
+        <v>0.391203164464152</v>
       </c>
       <c r="G1140" t="n">
         <v>30</v>
@@ -42515,7 +42710,7 @@
         <v>3</v>
       </c>
       <c r="F1141" t="n">
-        <v>0.3912031644641525</v>
+        <v>0.391203164464152</v>
       </c>
       <c r="G1141" t="n">
         <v>30</v>
@@ -42550,7 +42745,7 @@
         <v>3</v>
       </c>
       <c r="F1142" t="n">
-        <v>0.3912031644641525</v>
+        <v>0.391203164464152</v>
       </c>
       <c r="G1142" t="n">
         <v>30</v>
@@ -42585,7 +42780,7 @@
         <v>3</v>
       </c>
       <c r="F1143" t="n">
-        <v>0.3912031644641525</v>
+        <v>0.391203164464152</v>
       </c>
       <c r="G1143" t="n">
         <v>30</v>
@@ -42620,7 +42815,7 @@
         <v>3</v>
       </c>
       <c r="F1144" t="n">
-        <v>0.3912031644641525</v>
+        <v>0.391203164464152</v>
       </c>
       <c r="G1144" t="n">
         <v>30</v>
@@ -42655,7 +42850,7 @@
         <v>3</v>
       </c>
       <c r="F1145" t="n">
-        <v>0.3912031644641525</v>
+        <v>0.391203164464152</v>
       </c>
       <c r="G1145" t="n">
         <v>30</v>
@@ -42690,7 +42885,7 @@
         <v>3</v>
       </c>
       <c r="F1146" t="n">
-        <v>0.3912031644641525</v>
+        <v>0.391203164464152</v>
       </c>
       <c r="G1146" t="n">
         <v>30</v>
@@ -42725,7 +42920,7 @@
         <v>3</v>
       </c>
       <c r="F1147" t="n">
-        <v>0.3912031644641525</v>
+        <v>0.391203164464152</v>
       </c>
       <c r="G1147" t="n">
         <v>30</v>
@@ -42760,7 +42955,7 @@
         <v>3</v>
       </c>
       <c r="F1148" t="n">
-        <v>0.3912031644641525</v>
+        <v>0.391203164464152</v>
       </c>
       <c r="G1148" t="n">
         <v>30</v>
@@ -42795,7 +42990,7 @@
         <v>3</v>
       </c>
       <c r="F1149" t="n">
-        <v>0.3912031644641525</v>
+        <v>0.391203164464152</v>
       </c>
       <c r="G1149" t="n">
         <v>30</v>
@@ -42830,7 +43025,7 @@
         <v>2</v>
       </c>
       <c r="F1150" t="n">
-        <v>0.6681232381617422</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1150" t="n">
         <v>30</v>
@@ -42865,7 +43060,7 @@
         <v>2</v>
       </c>
       <c r="F1151" t="n">
-        <v>0.6681232381617422</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1151" t="n">
         <v>30</v>
@@ -42900,7 +43095,7 @@
         <v>2</v>
       </c>
       <c r="F1152" t="n">
-        <v>0.6681232381617422</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1152" t="n">
         <v>30</v>
@@ -42935,7 +43130,7 @@
         <v>2</v>
       </c>
       <c r="F1153" t="n">
-        <v>0.6681232381617422</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1153" t="n">
         <v>30</v>
@@ -42970,7 +43165,7 @@
         <v>2</v>
       </c>
       <c r="F1154" t="n">
-        <v>0.6681232381617422</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1154" t="n">
         <v>30</v>
@@ -43005,7 +43200,7 @@
         <v>2</v>
       </c>
       <c r="F1155" t="n">
-        <v>0.6681232381617422</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1155" t="n">
         <v>30</v>
@@ -43040,7 +43235,7 @@
         <v>2</v>
       </c>
       <c r="F1156" t="n">
-        <v>0.6681232381617422</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1156" t="n">
         <v>30</v>
@@ -43075,7 +43270,7 @@
         <v>2</v>
       </c>
       <c r="F1157" t="n">
-        <v>0.6681232381617422</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1157" t="n">
         <v>30</v>
@@ -43110,7 +43305,7 @@
         <v>2</v>
       </c>
       <c r="F1158" t="n">
-        <v>0.6681232381617422</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1158" t="n">
         <v>30</v>
@@ -43145,7 +43340,7 @@
         <v>2</v>
       </c>
       <c r="F1159" t="n">
-        <v>0.6681232381617422</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1159" t="n">
         <v>30</v>
@@ -43180,7 +43375,7 @@
         <v>2</v>
       </c>
       <c r="F1160" t="n">
-        <v>0.6681232381617422</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1160" t="n">
         <v>30</v>
@@ -43215,7 +43410,7 @@
         <v>2</v>
       </c>
       <c r="F1161" t="n">
-        <v>0.6681232381617422</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1161" t="n">
         <v>30</v>
@@ -43250,7 +43445,7 @@
         <v>2</v>
       </c>
       <c r="F1162" t="n">
-        <v>0.6681232381617422</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1162" t="n">
         <v>30</v>
@@ -43285,7 +43480,7 @@
         <v>2</v>
       </c>
       <c r="F1163" t="n">
-        <v>0.6681232381617422</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1163" t="n">
         <v>30</v>
@@ -43320,7 +43515,7 @@
         <v>3</v>
       </c>
       <c r="F1164" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1164" t="n">
         <v>30</v>
@@ -43355,7 +43550,7 @@
         <v>3</v>
       </c>
       <c r="F1165" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1165" t="n">
         <v>30</v>
@@ -43390,7 +43585,7 @@
         <v>3</v>
       </c>
       <c r="F1166" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1166" t="n">
         <v>30</v>
@@ -43425,7 +43620,7 @@
         <v>3</v>
       </c>
       <c r="F1167" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1167" t="n">
         <v>30</v>
@@ -43460,7 +43655,7 @@
         <v>3</v>
       </c>
       <c r="F1168" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1168" t="n">
         <v>30</v>
@@ -43495,7 +43690,7 @@
         <v>3</v>
       </c>
       <c r="F1169" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1169" t="n">
         <v>30</v>
@@ -43530,7 +43725,7 @@
         <v>3</v>
       </c>
       <c r="F1170" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1170" t="n">
         <v>30</v>
@@ -43565,7 +43760,7 @@
         <v>3</v>
       </c>
       <c r="F1171" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1171" t="n">
         <v>30</v>
@@ -43600,7 +43795,7 @@
         <v>3</v>
       </c>
       <c r="F1172" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1172" t="n">
         <v>30</v>
@@ -43635,7 +43830,7 @@
         <v>3</v>
       </c>
       <c r="F1173" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1173" t="n">
         <v>30</v>
@@ -43670,7 +43865,7 @@
         <v>3</v>
       </c>
       <c r="F1174" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1174" t="n">
         <v>30</v>
@@ -43705,7 +43900,7 @@
         <v>3</v>
       </c>
       <c r="F1175" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1175" t="n">
         <v>30</v>
@@ -43740,7 +43935,7 @@
         <v>3</v>
       </c>
       <c r="F1176" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1176" t="n">
         <v>30</v>
@@ -43775,7 +43970,7 @@
         <v>3</v>
       </c>
       <c r="F1177" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1177" t="n">
         <v>30</v>
@@ -43810,7 +44005,7 @@
         <v>2</v>
       </c>
       <c r="F1178" t="n">
-        <v>0.3495141428667713</v>
+        <v>0.3495141428667718</v>
       </c>
       <c r="G1178" t="n">
         <v>30</v>
@@ -43845,7 +44040,7 @@
         <v>2</v>
       </c>
       <c r="F1179" t="n">
-        <v>0.3495141428667713</v>
+        <v>0.3495141428667718</v>
       </c>
       <c r="G1179" t="n">
         <v>30</v>
@@ -43880,7 +44075,7 @@
         <v>2</v>
       </c>
       <c r="F1180" t="n">
-        <v>0.3495141428667713</v>
+        <v>0.3495141428667718</v>
       </c>
       <c r="G1180" t="n">
         <v>30</v>
@@ -43915,7 +44110,7 @@
         <v>2</v>
       </c>
       <c r="F1181" t="n">
-        <v>0.3495141428667713</v>
+        <v>0.3495141428667718</v>
       </c>
       <c r="G1181" t="n">
         <v>30</v>
@@ -43950,7 +44145,7 @@
         <v>2</v>
       </c>
       <c r="F1182" t="n">
-        <v>0.3495141428667713</v>
+        <v>0.3495141428667718</v>
       </c>
       <c r="G1182" t="n">
         <v>30</v>
@@ -43985,7 +44180,7 @@
         <v>2</v>
       </c>
       <c r="F1183" t="n">
-        <v>0.3495141428667713</v>
+        <v>0.3495141428667718</v>
       </c>
       <c r="G1183" t="n">
         <v>30</v>
@@ -44020,7 +44215,7 @@
         <v>2</v>
       </c>
       <c r="F1184" t="n">
-        <v>0.3495141428667713</v>
+        <v>0.3495141428667718</v>
       </c>
       <c r="G1184" t="n">
         <v>30</v>
@@ -44055,7 +44250,7 @@
         <v>2</v>
       </c>
       <c r="F1185" t="n">
-        <v>0.3495141428667713</v>
+        <v>0.3495141428667718</v>
       </c>
       <c r="G1185" t="n">
         <v>30</v>
@@ -44090,7 +44285,7 @@
         <v>2</v>
       </c>
       <c r="F1186" t="n">
-        <v>0.3495141428667713</v>
+        <v>0.3495141428667718</v>
       </c>
       <c r="G1186" t="n">
         <v>30</v>
@@ -44125,7 +44320,7 @@
         <v>2</v>
       </c>
       <c r="F1187" t="n">
-        <v>0.3495141428667713</v>
+        <v>0.3495141428667718</v>
       </c>
       <c r="G1187" t="n">
         <v>30</v>
@@ -44160,7 +44355,7 @@
         <v>2</v>
       </c>
       <c r="F1188" t="n">
-        <v>0.3495141428667713</v>
+        <v>0.3495141428667718</v>
       </c>
       <c r="G1188" t="n">
         <v>30</v>
@@ -44195,7 +44390,7 @@
         <v>2</v>
       </c>
       <c r="F1189" t="n">
-        <v>0.3495141428667713</v>
+        <v>0.3495141428667718</v>
       </c>
       <c r="G1189" t="n">
         <v>30</v>
@@ -44230,7 +44425,7 @@
         <v>2</v>
       </c>
       <c r="F1190" t="n">
-        <v>0.3495141428667713</v>
+        <v>0.3495141428667718</v>
       </c>
       <c r="G1190" t="n">
         <v>30</v>
@@ -44265,7 +44460,7 @@
         <v>2</v>
       </c>
       <c r="F1191" t="n">
-        <v>0.3495141428667713</v>
+        <v>0.3495141428667718</v>
       </c>
       <c r="G1191" t="n">
         <v>30</v>
@@ -46342,7 +46537,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -46388,7 +46583,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -46434,7 +46629,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far|node_effective_blocks|node_distinct_months|node_blocked_holdouts</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -46480,7 +46675,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>effective_blocks|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|blocked_holdouts|holdout_far|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -46526,7 +46721,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -46618,7 +46813,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far|node_effective_blocks|node_distinct_months|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -46664,7 +46859,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>effective_blocks|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|blocked_holdouts|holdout_far|node_blocked_holdouts</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -46756,7 +46951,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -46802,7 +46997,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far|node_effective_blocks|node_distinct_months|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -46848,7 +47043,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>effective_blocks|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|blocked_holdouts|holdout_far|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -46889,7 +47084,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>statistical_action_candidate</t>
+          <t>family_and_node_action_candidate</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -46940,7 +47135,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -46986,7 +47181,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -47032,7 +47227,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -47049,7 +47244,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -47073,12 +47268,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>statistical_action_candidate</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>node_holdout_far</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -47170,7 +47365,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -47216,7 +47411,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far|node_bootstrap_stability|node_blocked_holdouts</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -47257,7 +47452,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>statistical_action_candidate</t>
+          <t>family_and_node_action_candidate</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -47308,7 +47503,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -47354,7 +47549,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -47400,7 +47595,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -47417,7 +47612,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -47441,12 +47636,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>statistical_action_candidate</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>node_bootstrap_stability</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -47492,7 +47687,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_bootstrap_stability|node_holdout_far</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -47538,7 +47733,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -47584,7 +47779,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far|node_bootstrap_stability|node_blocked_holdouts</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -47630,7 +47825,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -47676,7 +47871,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_bootstrap_stability|node_holdout_far</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -47722,7 +47917,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -47768,7 +47963,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>effective_blocks|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|blocked_holdouts|holdout_far|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -47814,7 +48009,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -47860,7 +48055,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -47906,7 +48101,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -47952,7 +48147,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>effective_blocks|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|blocked_holdouts|holdout_far|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -47998,7 +48193,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -48044,7 +48239,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -48090,7 +48285,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far|node_effective_blocks|node_distinct_months|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -48136,7 +48331,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>effective_blocks|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|blocked_holdouts|holdout_far|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -48153,7 +48348,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -48177,12 +48372,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>statistical_action_candidate</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>node_holdout_far</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -48228,7 +48423,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -48274,7 +48469,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -48320,7 +48515,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far|node_blocked_holdouts</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -48361,7 +48556,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>statistical_action_candidate</t>
+          <t>family_and_node_action_candidate</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -48412,7 +48607,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -48458,7 +48653,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -48504,7 +48699,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -48521,7 +48716,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -48545,12 +48740,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>statistical_action_candidate</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>node_holdout_far</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -48596,7 +48791,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -48642,7 +48837,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -48688,7 +48883,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -48705,7 +48900,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -48729,12 +48924,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>statistical_action_candidate</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>node_holdout_far</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -48780,7 +48975,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -48826,7 +49021,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -48872,7 +49067,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far|node_bootstrap_stability|node_blocked_holdouts</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -48984,7 +49179,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -49030,7 +49225,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -49076,7 +49271,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far|node_effective_blocks|node_distinct_months|node_blocked_holdouts</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -49122,7 +49317,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>effective_blocks|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|blocked_holdouts|holdout_far|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -49168,7 +49363,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -49260,7 +49455,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far|node_effective_blocks|node_distinct_months|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -49306,7 +49501,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>effective_blocks|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|blocked_holdouts|holdout_far|node_blocked_holdouts</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -49398,7 +49593,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -49444,7 +49639,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far|node_effective_blocks|node_distinct_months|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -49490,7 +49685,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>effective_blocks|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|blocked_holdouts|holdout_far|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -49531,7 +49726,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>statistical_action_candidate</t>
+          <t>family_and_node_action_candidate</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -49582,7 +49777,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -49628,7 +49823,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -49674,7 +49869,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -49691,7 +49886,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -49715,12 +49910,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>statistical_action_candidate</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>node_holdout_far</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -49812,7 +50007,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -49858,7 +50053,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far|node_bootstrap_stability|node_blocked_holdouts</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -49899,7 +50094,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>statistical_action_candidate</t>
+          <t>family_and_node_action_candidate</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -49950,7 +50145,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -49996,7 +50191,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -50042,7 +50237,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -50059,7 +50254,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -50083,12 +50278,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>statistical_action_candidate</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>node_bootstrap_stability</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -50134,7 +50329,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_bootstrap_stability|node_holdout_far</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -50180,7 +50375,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -50226,7 +50421,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far|node_bootstrap_stability|node_blocked_holdouts</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -50272,7 +50467,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -50318,7 +50513,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_bootstrap_stability|node_holdout_far</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -50364,7 +50559,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -50410,7 +50605,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>effective_blocks|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|blocked_holdouts|holdout_far|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -50456,7 +50651,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -50502,7 +50697,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -50548,7 +50743,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -50594,7 +50789,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>effective_blocks|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|blocked_holdouts|holdout_far|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -50640,7 +50835,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -50686,7 +50881,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -50732,7 +50927,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far|node_effective_blocks|node_distinct_months|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -50778,7 +50973,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>effective_blocks|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|blocked_holdouts|holdout_far|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -50795,7 +50990,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -50819,12 +51014,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>statistical_action_candidate</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>node_holdout_far</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -50870,7 +51065,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -50916,7 +51111,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -50962,7 +51157,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far|node_blocked_holdouts</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -51003,7 +51198,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>statistical_action_candidate</t>
+          <t>family_and_node_action_candidate</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -51054,7 +51249,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -51100,7 +51295,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -51146,7 +51341,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -51163,7 +51358,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -51187,12 +51382,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>statistical_action_candidate</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>node_holdout_far</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -51238,7 +51433,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -51284,7 +51479,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -51330,7 +51525,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -51347,7 +51542,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -51371,12 +51566,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>statistical_action_candidate</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>node_holdout_far</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -51422,7 +51617,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>holdout_far</t>
+          <t>holdout_far|node_holdout_far</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -51468,7 +51663,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -51514,7 +51709,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far|node_bootstrap_stability|node_blocked_holdouts</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -51852,7 +52047,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d7-d6-v2.2</t>
+          <t>d7-d6-v2.3</t>
         </is>
       </c>
       <c r="B2" t="n">
